--- a/backend/templates/plantilla-liquidacion.xlsx
+++ b/backend/templates/plantilla-liquidacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\facturas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\seminario_2026\TechAssist\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7BE0ED-A1BF-42F0-AA83-1D63EDBA3C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB4552C-7622-455F-A647-BD140140F5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="100">
   <si>
     <t>IDP</t>
   </si>
@@ -348,9 +348,6 @@
     <t>LUNES</t>
   </si>
   <si>
-    <t>ERICK ESTUARDO MEJIA HERNANDEZ</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -360,232 +357,16 @@
     <t>MIÉRCOLES</t>
   </si>
   <si>
-    <t>ALTA VERAPAZ</t>
-  </si>
-  <si>
-    <t>LA TINTA</t>
-  </si>
-  <si>
-    <t>DF-LA-TINTA-4397</t>
-  </si>
-  <si>
-    <t>TACTIC</t>
-  </si>
-  <si>
-    <t>DF-TACTIC-4155</t>
-  </si>
-  <si>
-    <t>SAN CRISTOBAL</t>
-  </si>
-  <si>
-    <t>DF-SANCRIS-4184</t>
-  </si>
-  <si>
-    <t>COBAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANTA CRUZ </t>
-  </si>
-  <si>
-    <t>DF-SANTA-CRUZ-1102</t>
-  </si>
-  <si>
-    <t>MD-COBAN-4343</t>
-  </si>
-  <si>
-    <t>PAIZ-COBAN-491</t>
-  </si>
-  <si>
-    <t>CARCHA</t>
-  </si>
-  <si>
-    <t>DF-CARCHA-194</t>
-  </si>
-  <si>
-    <t>INC54383252</t>
-  </si>
-  <si>
-    <t>INC54466481</t>
-  </si>
-  <si>
-    <t>BAJA VERAPAZ</t>
-  </si>
-  <si>
-    <t>RABINAL</t>
-  </si>
-  <si>
-    <t>DF-RABINAL-4080</t>
-  </si>
-  <si>
-    <t>INC54464795</t>
-  </si>
-  <si>
-    <t>INC54466403</t>
-  </si>
-  <si>
-    <t>INC54479690</t>
-  </si>
-  <si>
-    <t>INC54481722</t>
-  </si>
-  <si>
-    <t>INC54469083</t>
-  </si>
-  <si>
-    <t>INC54469093</t>
-  </si>
-  <si>
-    <t>INC54476244</t>
-  </si>
-  <si>
-    <t>INC54477248</t>
-  </si>
-  <si>
-    <t>INC54479557</t>
-  </si>
-  <si>
-    <t>INC54485917</t>
-  </si>
-  <si>
-    <t>INC54475535</t>
-  </si>
-  <si>
-    <t>INC54475538</t>
-  </si>
-  <si>
-    <t>INC54501127</t>
-  </si>
-  <si>
-    <t>INC54507784</t>
-  </si>
-  <si>
-    <t>INC54503487</t>
-  </si>
-  <si>
-    <t>INC54533132</t>
-  </si>
-  <si>
-    <t>INC54502453</t>
-  </si>
-  <si>
-    <t>INC54535339</t>
-  </si>
-  <si>
-    <t>INC54535408</t>
-  </si>
-  <si>
-    <t>INC54201336</t>
-  </si>
-  <si>
-    <t>INC54518953</t>
-  </si>
-  <si>
-    <t>INC54535837</t>
-  </si>
-  <si>
-    <t>INC54520238</t>
-  </si>
-  <si>
-    <t>INC54364335</t>
-  </si>
-  <si>
-    <t>INC54551524</t>
-  </si>
-  <si>
-    <t>REVISION DE CAJAS SOBRE PROBLEMAS CON PJNPAD</t>
-  </si>
-  <si>
-    <t>REPARACION DE SCO SOBRE MODULO BCR EN TIENDA</t>
-  </si>
-  <si>
-    <t>SOLICTUD DE BASCULA DE PERECDEROS EN TIENDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUIA A USUARIO A VALIDACION DE SCO SOBRE ATASCO DE MONEDA EN BCR </t>
-  </si>
-  <si>
-    <t>CAMBIO Y CONFIGURACION DE IMPRESORA PORTATIL</t>
-  </si>
-  <si>
-    <t>REVISON DE ESCANER BASCULA DEL AREA DE CAJAS</t>
-  </si>
-  <si>
-    <t>REVISION DE SCO SOBRE HOPER DE Q1</t>
-  </si>
-  <si>
-    <t>REPARACION DE SCO SOBRE ATASCO DE MODULO BNR</t>
-  </si>
-  <si>
-    <t>REVISION DE SCO SOBRE TOPMODULE ATASCO Y DAÑO DE MECANISMO SOLICITUD DE PARTE</t>
-  </si>
-  <si>
-    <t>PETICION DE HOPER DE Q0,50 EN TIENDA</t>
-  </si>
-  <si>
-    <t>VALIDACION DE ARS EN TIENDA VIA RCA</t>
-  </si>
-  <si>
-    <t>REPARACION DE SCO SOBRE ATASCO EN MECANISMO BNR Y BCR</t>
-  </si>
-  <si>
-    <t>REPARACION DE SCO SOBRE ATASCO EN BNR</t>
-  </si>
-  <si>
-    <t>VALIDACION DE ARS EN TIENDA VALIDACION DE SISTEMA</t>
-  </si>
-  <si>
-    <t>REVISION DE HHC EN TIENDA</t>
-  </si>
-  <si>
-    <t>REPARACION DE CAJA  SOBRE SISTEMA Y CPU POS</t>
-  </si>
-  <si>
-    <t>REPARACION DE SCO Y CAMBIO DE TOPMODULE</t>
-  </si>
-  <si>
-    <t>CAMBIO DE MONITOR DEL AREA DE CAJAS</t>
-  </si>
-  <si>
-    <t>REPARACION DE MONITOR DEL AREA DE GERENCIA</t>
-  </si>
-  <si>
-    <t>CAMBIO DE ESCANER BASCULA Y CONFIGURACION</t>
-  </si>
-  <si>
-    <t>CAMBIO DE HOPER DE Q1</t>
-  </si>
-  <si>
-    <t>CAMBIO DE HOPER DE Q0,50</t>
-  </si>
-  <si>
-    <t>REPARACION DE SCO SOBRE ATASCO EN MODULO BCR</t>
-  </si>
-  <si>
-    <t>REPARACION DE BASCULAS DE SCO EN TIENDA</t>
-  </si>
-  <si>
-    <t>REPARACION VIA RCA DE BASCULA DE PERECEDEROS</t>
-  </si>
-  <si>
-    <t>CAMBIO DE BASCULA DE PERECEDEROS EN TIENDA</t>
-  </si>
-  <si>
-    <t>REVISION DE SCO SOBRE ATASCO DE HOPER DE Q1</t>
-  </si>
-  <si>
-    <t>REPARACION DE SCO SOBRE MODULO BNR, CAMBIO DE RECICLYNG</t>
-  </si>
-  <si>
-    <t>INC54559125</t>
-  </si>
-  <si>
-    <t>INC54561194</t>
-  </si>
-  <si>
-    <t>REVISION DE SCO SOBRE TOPMODULE EN TIENDA ATASCO EN MECASNISMO Y DAÑO EN PARTE</t>
-  </si>
-  <si>
-    <t>REVISION DE HOPER DE Q0,50 EN TIENDA SOBRE ATASCO DE MECANISMO</t>
+    <t>CODIGO EMPLEADO</t>
+  </si>
+  <si>
+    <t>0/00/2026</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>NOMBRE TECNICO</t>
   </si>
 </sst>
 </file>
@@ -1916,251 +1697,6 @@
     <xf numFmtId="49" fontId="8" fillId="3" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="3" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2199,7 +1735,252 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="3" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2769,14 +2550,14 @@
     <row r="1" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="116" t="s">
+      <c r="C1" s="166" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
       <c r="I1" s="33"/>
       <c r="J1" s="50"/>
       <c r="K1" s="50"/>
@@ -2786,14 +2567,14 @@
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="34"/>
-      <c r="C2" s="117" t="s">
+      <c r="C2" s="167" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
+      <c r="H2" s="167"/>
       <c r="J2" s="52"/>
       <c r="K2" s="52"/>
       <c r="L2" s="52"/>
@@ -2816,12 +2597,12 @@
     <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="35"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
       <c r="I4" s="38"/>
       <c r="J4" s="38"/>
       <c r="K4" s="38"/>
@@ -2831,14 +2612,14 @@
     <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="35"/>
-      <c r="C5" s="166" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="166"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="166"/>
+      <c r="C5" s="133" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
       <c r="I5" s="35"/>
       <c r="J5" s="38"/>
       <c r="K5" s="38"/>
@@ -2848,99 +2629,99 @@
     <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="35"/>
-      <c r="C6" s="166"/>
-      <c r="D6" s="166"/>
-      <c r="E6" s="166"/>
-      <c r="F6" s="166"/>
-      <c r="G6" s="166"/>
-      <c r="H6" s="166"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
       <c r="I6" s="35"/>
-      <c r="J6" s="160" t="s">
+      <c r="J6" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="160"/>
-      <c r="L6" s="161">
-        <v>46242</v>
-      </c>
-      <c r="M6" s="162"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="129"/>
     </row>
     <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="35"/>
-      <c r="C7" s="165">
-        <v>6556</v>
-      </c>
-      <c r="D7" s="165"/>
-      <c r="E7" s="165"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="165"/>
+      <c r="C7" s="132" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
       <c r="I7" s="35"/>
-      <c r="J7" s="160" t="s">
+      <c r="J7" s="127" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="160"/>
-      <c r="L7" s="163">
-        <v>0</v>
-      </c>
-      <c r="M7" s="164"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="130">
+        <v>0</v>
+      </c>
+      <c r="M7" s="131"/>
     </row>
     <row r="8" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
       <c r="I8" s="35"/>
-      <c r="J8" s="114" t="s">
+      <c r="J8" s="164" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="115"/>
+      <c r="K8" s="164"/>
+      <c r="L8" s="164"/>
+      <c r="M8" s="165"/>
     </row>
     <row r="9" spans="1:13" s="31" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="126" t="s">
+      <c r="A9" s="176" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="127"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="128" t="s">
+      <c r="B9" s="177"/>
+      <c r="C9" s="177"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="177"/>
+      <c r="F9" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="129"/>
-      <c r="K9" s="129"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="131" t="s">
+      <c r="G9" s="179"/>
+      <c r="H9" s="179"/>
+      <c r="I9" s="179"/>
+      <c r="J9" s="179"/>
+      <c r="K9" s="179"/>
+      <c r="L9" s="180"/>
+      <c r="M9" s="181" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="134" t="s">
+      <c r="A10" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="134" t="s">
+      <c r="B10" s="184" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="134" t="s">
+      <c r="C10" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="134" t="s">
+      <c r="D10" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="136" t="s">
+      <c r="E10" s="186" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G10" s="74" t="s">
         <v>88</v>
@@ -2952,7 +2733,7 @@
         <v>89</v>
       </c>
       <c r="J10" s="74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K10" s="74" t="s">
         <v>90</v>
@@ -2960,14 +2741,14 @@
       <c r="L10" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="M10" s="132"/>
+      <c r="M10" s="182"/>
     </row>
     <row r="11" spans="1:13" s="8" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="135"/>
-      <c r="B11" s="135"/>
-      <c r="C11" s="135"/>
-      <c r="D11" s="135"/>
-      <c r="E11" s="137"/>
+      <c r="A11" s="185"/>
+      <c r="B11" s="185"/>
+      <c r="C11" s="185"/>
+      <c r="D11" s="185"/>
+      <c r="E11" s="187"/>
       <c r="F11" s="75">
         <v>46242</v>
       </c>
@@ -2995,7 +2776,7 @@
         <f t="shared" si="0"/>
         <v>46248</v>
       </c>
-      <c r="M11" s="133"/>
+      <c r="M11" s="183"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
@@ -3186,20 +2967,18 @@
       </c>
       <c r="E18" s="12">
         <f>+M18/1.12</f>
-        <v>4.4642857142857135</v>
+        <v>0</v>
       </c>
       <c r="F18" s="81"/>
       <c r="G18" s="82"/>
       <c r="H18" s="82"/>
       <c r="I18" s="82"/>
-      <c r="J18" s="82">
-        <v>5</v>
-      </c>
+      <c r="J18" s="82"/>
       <c r="K18" s="82"/>
       <c r="L18" s="83"/>
       <c r="M18" s="13">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -3304,24 +3083,18 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="2"/>
-        <v>165.17857142857142</v>
+        <v>0</v>
       </c>
       <c r="F22" s="81"/>
       <c r="G22" s="82"/>
       <c r="H22" s="82"/>
-      <c r="I22" s="82">
-        <v>85</v>
-      </c>
-      <c r="J22" s="82">
-        <v>50</v>
-      </c>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
       <c r="K22" s="82"/>
-      <c r="L22" s="83">
-        <v>50</v>
-      </c>
+      <c r="L22" s="83"/>
       <c r="M22" s="13">
         <f t="shared" si="1"/>
-        <v>185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -3484,33 +3257,33 @@
       </c>
       <c r="E28" s="62">
         <f>(+E26+E25+E22+E21+E17+E15+E14+E13+E12+E19+E27+E18+E23+E24)*0.12</f>
-        <v>20.357142857142858</v>
-      </c>
-      <c r="F28" s="123"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="124"/>
-      <c r="J28" s="124"/>
-      <c r="K28" s="124"/>
-      <c r="L28" s="124"/>
-      <c r="M28" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="173"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="174"/>
+      <c r="L28" s="174"/>
+      <c r="M28" s="175"/>
     </row>
     <row r="29" spans="1:14" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="118" t="s">
+      <c r="A29" s="168" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="119"/>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="121"/>
-      <c r="H29" s="121"/>
-      <c r="I29" s="121"/>
-      <c r="J29" s="121"/>
-      <c r="K29" s="121"/>
-      <c r="L29" s="121"/>
-      <c r="M29" s="122"/>
+      <c r="B29" s="169"/>
+      <c r="C29" s="169"/>
+      <c r="D29" s="169"/>
+      <c r="E29" s="169"/>
+      <c r="F29" s="170"/>
+      <c r="G29" s="171"/>
+      <c r="H29" s="171"/>
+      <c r="I29" s="171"/>
+      <c r="J29" s="171"/>
+      <c r="K29" s="171"/>
+      <c r="L29" s="171"/>
+      <c r="M29" s="172"/>
       <c r="N29" s="16"/>
     </row>
     <row r="30" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -3981,13 +3754,13 @@
       <c r="N45" s="3"/>
     </row>
     <row r="46" spans="1:14" s="7" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="148"/>
-      <c r="B46" s="149"/>
-      <c r="C46" s="149"/>
-      <c r="D46" s="150"/>
+      <c r="A46" s="153"/>
+      <c r="B46" s="154"/>
+      <c r="C46" s="154"/>
+      <c r="D46" s="155"/>
       <c r="E46" s="63">
         <f>+E12+E13+E14+E15+E16+E17+E19+E20+E21+E22+E25+E26+E28+E30+E31+E32+E33+E34+E35+E41+E42+E43+E44+E45+E23+E24+E27+E36+E40+E37+E38+E39+E18</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F46" s="64">
         <f>SUM(F12:F45)</f>
@@ -4003,11 +3776,11 @@
       </c>
       <c r="I46" s="64">
         <f t="shared" si="5"/>
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="J46" s="64">
         <f t="shared" si="5"/>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K46" s="64">
         <f t="shared" si="5"/>
@@ -4015,111 +3788,111 @@
       </c>
       <c r="L46" s="64">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M46" s="65">
         <f>SUM(M12:M45)</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="N46" s="3"/>
     </row>
     <row r="47" spans="1:14" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A47" s="151" t="s">
+      <c r="A47" s="156" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="152"/>
-      <c r="C47" s="155"/>
-      <c r="D47" s="155"/>
-      <c r="E47" s="155"/>
-      <c r="F47" s="155"/>
-      <c r="G47" s="155"/>
-      <c r="H47" s="155"/>
-      <c r="I47" s="155"/>
-      <c r="J47" s="155"/>
-      <c r="K47" s="155"/>
-      <c r="L47" s="155"/>
-      <c r="M47" s="156"/>
+      <c r="B47" s="157"/>
+      <c r="C47" s="160"/>
+      <c r="D47" s="160"/>
+      <c r="E47" s="160"/>
+      <c r="F47" s="160"/>
+      <c r="G47" s="160"/>
+      <c r="H47" s="160"/>
+      <c r="I47" s="160"/>
+      <c r="J47" s="160"/>
+      <c r="K47" s="160"/>
+      <c r="L47" s="160"/>
+      <c r="M47" s="161"/>
       <c r="N47" s="3"/>
     </row>
     <row r="48" spans="1:14" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="153"/>
-      <c r="B48" s="154"/>
-      <c r="C48" s="157"/>
-      <c r="D48" s="157"/>
-      <c r="E48" s="157"/>
-      <c r="F48" s="157"/>
-      <c r="G48" s="157"/>
-      <c r="H48" s="157"/>
-      <c r="I48" s="157"/>
-      <c r="J48" s="157"/>
-      <c r="K48" s="157"/>
-      <c r="L48" s="157"/>
-      <c r="M48" s="158"/>
+      <c r="A48" s="158"/>
+      <c r="B48" s="159"/>
+      <c r="C48" s="162"/>
+      <c r="D48" s="162"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="162"/>
+      <c r="G48" s="162"/>
+      <c r="H48" s="162"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="162"/>
+      <c r="K48" s="162"/>
+      <c r="L48" s="162"/>
+      <c r="M48" s="163"/>
     </row>
     <row r="49" spans="1:13" s="7" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="139" t="s">
+      <c r="A49" s="144" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="140"/>
-      <c r="C49" s="140"/>
-      <c r="D49" s="140"/>
-      <c r="E49" s="140"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="140"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="140"/>
-      <c r="K49" s="140"/>
-      <c r="L49" s="140"/>
-      <c r="M49" s="141"/>
+      <c r="B49" s="145"/>
+      <c r="C49" s="145"/>
+      <c r="D49" s="145"/>
+      <c r="E49" s="145"/>
+      <c r="F49" s="145"/>
+      <c r="G49" s="145"/>
+      <c r="H49" s="145"/>
+      <c r="I49" s="145"/>
+      <c r="J49" s="145"/>
+      <c r="K49" s="145"/>
+      <c r="L49" s="145"/>
+      <c r="M49" s="146"/>
     </row>
     <row r="50" spans="1:13" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="142" t="str">
+      <c r="A50" s="147" t="str">
         <f>+CONCATENATE(KILOMETRAJE!F15," ",KILOMETRAJE!G15," ",KILOMETRAJE!F16," ",KILOMETRAJE!G16," ",KILOMETRAJE!F17," ",KILOMETRAJE!G17," ",KILOMETRAJE!F18," ",KILOMETRAJE!G18," ",KILOMETRAJE!F19," ",KILOMETRAJE!G19," ",KILOMETRAJE!F20," ",KILOMETRAJE!G20," ",KILOMETRAJE!F21," ",KILOMETRAJE!G21," ",KILOMETRAJE!F22," ",KILOMETRAJE!G22," ",KILOMETRAJE!F23," ",KILOMETRAJE!G23," ",KILOMETRAJE!F24," ",KILOMETRAJE!G24," ",KILOMETRAJE!F25," ",KILOMETRAJE!G25," ",KILOMETRAJE!F26," ",KILOMETRAJE!G26," ",KILOMETRAJE!F27," ",KILOMETRAJE!G27," ",KILOMETRAJE!F28," ",KILOMETRAJE!G28," ",KILOMETRAJE!F29," ",KILOMETRAJE!G29," ",KILOMETRAJE!F30," ",KILOMETRAJE!G30," ",KILOMETRAJE!F31," ",KILOMETRAJE!G31," ",KILOMETRAJE!F32," ",KILOMETRAJE!G32," ",KILOMETRAJE!F33," ",KILOMETRAJE!G33," ",KILOMETRAJE!F34," ",KILOMETRAJE!G34," ",KILOMETRAJE!F35," ",KILOMETRAJE!G35," ",KILOMETRAJE!F224," ",KILOMETRAJE!G36," ",KILOMETRAJE!F37," ",KILOMETRAJE!G37," ",KILOMETRAJE!F38," ",KILOMETRAJE!G38," ",KILOMETRAJE!F39," ",KILOMETRAJE!G39," ",KILOMETRAJE!F40," ",KILOMETRAJE!G40," ",KILOMETRAJE!F41," ",KILOMETRAJE!G41," ",KILOMETRAJE!F42," ",KILOMETRAJE!G42," ",KILOMETRAJE!F49," ",KILOMETRAJE!G49," ",KILOMETRAJE!F50," ",KILOMETRAJE!G50," ",)</f>
-        <v xml:space="preserve">DF-LA-TINTA-4397 INC54464795 DF-LA-TINTA-4397 INC54466403 DF-LA-TINTA-4397 INC54479690 DF-LA-TINTA-4397 INC54481722 MD-COBAN-4343 INC54469083 MD-COBAN-4343 INC54469093 MD-COBAN-4343 INC54476244 DF-SANTA-CRUZ-1102 INC54477248 DF-TACTIC-4155 INC54479557 DF-TACTIC-4155 INC54485917 DF-RABINAL-4080 INC54475535 DF-RABINAL-4080 INC54475538 DF-SANTA-CRUZ-1102 INC54501127 DF-LA-TINTA-4397 INC54507784 DF-LA-TINTA-4397 INC54481722 DF-SANTA-CRUZ-1102 INC54501127 MD-COBAN-4343 INC54503487 DF-TACTIC-4155 INC54533132 DF-TACTIC-4155 INC54485917 DF-SANCRIS-4184 INC54502453 DF-SANCRIS-4184 INC54535339  INC54535408 DF-SANCRIS-4184 INC54201336 DF-SANCRIS-4184 INC54383252 PAIZ-COBAN-491 INC54518953 MD-COBAN-4343 INC54535837 DF-LA-TINTA-4397 INC54520238 MD-COBAN-4343 INC54364335     </v>
-      </c>
-      <c r="B50" s="143"/>
-      <c r="C50" s="143"/>
-      <c r="D50" s="143"/>
-      <c r="E50" s="143"/>
-      <c r="F50" s="143"/>
-      <c r="G50" s="143"/>
-      <c r="H50" s="143"/>
-      <c r="I50" s="143"/>
-      <c r="J50" s="143"/>
-      <c r="K50" s="143"/>
-      <c r="L50" s="143"/>
-      <c r="M50" s="144"/>
+        <v xml:space="preserve">                                                            </v>
+      </c>
+      <c r="B50" s="148"/>
+      <c r="C50" s="148"/>
+      <c r="D50" s="148"/>
+      <c r="E50" s="148"/>
+      <c r="F50" s="148"/>
+      <c r="G50" s="148"/>
+      <c r="H50" s="148"/>
+      <c r="I50" s="148"/>
+      <c r="J50" s="148"/>
+      <c r="K50" s="148"/>
+      <c r="L50" s="148"/>
+      <c r="M50" s="149"/>
     </row>
     <row r="51" spans="1:13" s="7" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="142"/>
-      <c r="B51" s="143"/>
-      <c r="C51" s="143"/>
-      <c r="D51" s="143"/>
-      <c r="E51" s="143"/>
-      <c r="F51" s="143"/>
-      <c r="G51" s="143"/>
-      <c r="H51" s="143"/>
-      <c r="I51" s="143"/>
-      <c r="J51" s="143"/>
-      <c r="K51" s="143"/>
-      <c r="L51" s="143"/>
-      <c r="M51" s="144"/>
+      <c r="A51" s="147"/>
+      <c r="B51" s="148"/>
+      <c r="C51" s="148"/>
+      <c r="D51" s="148"/>
+      <c r="E51" s="148"/>
+      <c r="F51" s="148"/>
+      <c r="G51" s="148"/>
+      <c r="H51" s="148"/>
+      <c r="I51" s="148"/>
+      <c r="J51" s="148"/>
+      <c r="K51" s="148"/>
+      <c r="L51" s="148"/>
+      <c r="M51" s="149"/>
     </row>
     <row r="52" spans="1:13" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="145"/>
-      <c r="B52" s="146"/>
-      <c r="C52" s="146"/>
-      <c r="D52" s="146"/>
-      <c r="E52" s="146"/>
-      <c r="F52" s="146"/>
-      <c r="G52" s="146"/>
-      <c r="H52" s="146"/>
-      <c r="I52" s="146"/>
-      <c r="J52" s="146"/>
-      <c r="K52" s="146"/>
-      <c r="L52" s="146"/>
-      <c r="M52" s="147"/>
+      <c r="A52" s="150"/>
+      <c r="B52" s="151"/>
+      <c r="C52" s="151"/>
+      <c r="D52" s="151"/>
+      <c r="E52" s="151"/>
+      <c r="F52" s="151"/>
+      <c r="G52" s="151"/>
+      <c r="H52" s="151"/>
+      <c r="I52" s="151"/>
+      <c r="J52" s="151"/>
+      <c r="K52" s="151"/>
+      <c r="L52" s="151"/>
+      <c r="M52" s="152"/>
     </row>
     <row r="53" spans="1:13" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="26"/>
@@ -4192,42 +3965,42 @@
       <c r="A58" s="30"/>
       <c r="B58" s="29"/>
       <c r="C58" s="22"/>
-      <c r="F58" s="138" t="s">
+      <c r="F58" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="G58" s="138"/>
-      <c r="H58" s="138"/>
-      <c r="I58" s="138"/>
-      <c r="J58" s="138"/>
-      <c r="K58" s="138"/>
-      <c r="L58" s="138"/>
-      <c r="M58" s="138"/>
+      <c r="G58" s="134"/>
+      <c r="H58" s="134"/>
+      <c r="I58" s="134"/>
+      <c r="J58" s="134"/>
+      <c r="K58" s="134"/>
+      <c r="L58" s="134"/>
+      <c r="M58" s="134"/>
     </row>
     <row r="59" spans="1:13" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A59" s="30"/>
-      <c r="B59" s="171" t="str">
+      <c r="B59" s="139" t="str">
         <f>C5</f>
-        <v>ERICK ESTUARDO MEJIA HERNANDEZ</v>
-      </c>
-      <c r="C59" s="171"/>
-      <c r="F59" s="171" t="s">
+        <v>NOMBRE</v>
+      </c>
+      <c r="C59" s="139"/>
+      <c r="F59" s="139" t="s">
         <v>77</v>
       </c>
-      <c r="G59" s="171"/>
-      <c r="H59" s="171"/>
-      <c r="I59" s="171"/>
-      <c r="J59" s="171"/>
-      <c r="K59" s="171"/>
-      <c r="L59" s="171"/>
-      <c r="M59" s="171"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="139"/>
+      <c r="L59" s="139"/>
+      <c r="M59" s="139"/>
     </row>
     <row r="60" spans="1:13" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="30"/>
-      <c r="B60" s="138">
+      <c r="B60" s="134" t="str">
         <f>C7</f>
-        <v>6556</v>
-      </c>
-      <c r="C60" s="138"/>
+        <v>CODIGO EMPLEADO</v>
+      </c>
+      <c r="C60" s="134"/>
       <c r="F60" s="30"/>
       <c r="G60" s="30"/>
       <c r="H60" s="30"/>
@@ -4267,12 +4040,12 @@
       <c r="M63" s="7"/>
     </row>
     <row r="64" spans="1:13" ht="14.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="167" t="s">
+      <c r="B64" s="135" t="s">
         <v>46</v>
       </c>
-      <c r="C64" s="168"/>
-      <c r="D64" s="171"/>
-      <c r="E64" s="171"/>
+      <c r="C64" s="136"/>
+      <c r="D64" s="139"/>
+      <c r="E64" s="139"/>
       <c r="H64" s="30"/>
       <c r="I64" s="30"/>
       <c r="J64" s="30"/>
@@ -4281,10 +4054,10 @@
       <c r="M64" s="7"/>
     </row>
     <row r="65" spans="2:13" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="169"/>
-      <c r="C65" s="170"/>
-      <c r="D65" s="171"/>
-      <c r="E65" s="171"/>
+      <c r="B65" s="137"/>
+      <c r="C65" s="138"/>
+      <c r="D65" s="139"/>
+      <c r="E65" s="139"/>
       <c r="H65" s="30"/>
       <c r="I65" s="30"/>
       <c r="J65" s="30"/>
@@ -4293,37 +4066,37 @@
       <c r="M65" s="7"/>
     </row>
     <row r="66" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="172"/>
-      <c r="C66" s="173"/>
-      <c r="F66" s="138" t="s">
+      <c r="B66" s="140"/>
+      <c r="C66" s="141"/>
+      <c r="F66" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="G66" s="138"/>
-      <c r="H66" s="138"/>
-      <c r="I66" s="138"/>
-      <c r="J66" s="138"/>
-      <c r="K66" s="138"/>
-      <c r="L66" s="138"/>
-      <c r="M66" s="138"/>
+      <c r="G66" s="134"/>
+      <c r="H66" s="134"/>
+      <c r="I66" s="134"/>
+      <c r="J66" s="134"/>
+      <c r="K66" s="134"/>
+      <c r="L66" s="134"/>
+      <c r="M66" s="134"/>
     </row>
     <row r="67" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="174"/>
-      <c r="C67" s="175"/>
-      <c r="H67" s="171" t="s">
+      <c r="B67" s="142"/>
+      <c r="C67" s="143"/>
+      <c r="H67" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="I67" s="171"/>
-      <c r="J67" s="171"/>
-      <c r="K67" s="171"/>
+      <c r="I67" s="139"/>
+      <c r="J67" s="139"/>
+      <c r="K67" s="139"/>
       <c r="L67" s="41"/>
       <c r="M67" s="41"/>
     </row>
     <row r="68" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D68" s="159"/>
-      <c r="E68" s="159"/>
-      <c r="F68" s="159"/>
-      <c r="G68" s="159"/>
-      <c r="H68" s="159"/>
+      <c r="D68" s="126"/>
+      <c r="E68" s="126"/>
+      <c r="F68" s="126"/>
+      <c r="G68" s="126"/>
+      <c r="H68" s="126"/>
       <c r="I68" s="37"/>
       <c r="J68" s="37"/>
       <c r="K68" s="37"/>
@@ -4331,22 +4104,44 @@
       <c r="M68" s="37"/>
     </row>
     <row r="69" spans="2:13" ht="15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="159"/>
-      <c r="E69" s="159"/>
-      <c r="F69" s="159"/>
-      <c r="G69" s="159"/>
-      <c r="H69" s="159"/>
+      <c r="D69" s="126"/>
+      <c r="E69" s="126"/>
+      <c r="F69" s="126"/>
+      <c r="G69" s="126"/>
+      <c r="H69" s="126"/>
     </row>
     <row r="70" spans="2:13" ht="15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="159"/>
-      <c r="E70" s="159"/>
-      <c r="F70" s="159"/>
-      <c r="G70" s="159"/>
-      <c r="H70" s="159"/>
+      <c r="D70" s="126"/>
+      <c r="E70" s="126"/>
+      <c r="F70" s="126"/>
+      <c r="G70" s="126"/>
+      <c r="H70" s="126"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="38">
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="A49:M49"/>
+    <mergeCell ref="A50:M52"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A47:B48"/>
+    <mergeCell ref="C47:M47"/>
+    <mergeCell ref="C48:M48"/>
     <mergeCell ref="D68:H70"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L6:M6"/>
@@ -4363,28 +4158,6 @@
     <mergeCell ref="H67:K67"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="F59:M59"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="A49:M49"/>
-    <mergeCell ref="A50:M52"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A47:B48"/>
-    <mergeCell ref="C47:M47"/>
-    <mergeCell ref="C48:M48"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
@@ -4428,14 +4201,14 @@
     <row r="5" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="117" t="s">
+      <c r="D5" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="167"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -4445,14 +4218,14 @@
     <row r="6" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="167" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="167"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="167"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -4477,12 +4250,12 @@
     <row r="8" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="185">
-        <v>6556</v>
-      </c>
-      <c r="E8" s="185"/>
-      <c r="F8" s="185"/>
-      <c r="G8" s="185"/>
+      <c r="D8" s="190" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="190"/>
+      <c r="F8" s="190"/>
+      <c r="G8" s="190"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -4494,12 +4267,12 @@
     <row r="9" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="186" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="186"/>
-      <c r="F9" s="186"/>
-      <c r="G9" s="186"/>
+      <c r="D9" s="191" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="191"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="191"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -4511,12 +4284,12 @@
     <row r="10" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="187" t="s">
+      <c r="D10" s="192" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="187"/>
-      <c r="F10" s="187"/>
-      <c r="G10" s="187"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="192"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -4554,10 +4327,10 @@
     <row r="13" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="68"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="176" t="s">
+      <c r="D13" s="196" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="176" t="s">
+      <c r="E13" s="196" t="s">
         <v>68</v>
       </c>
       <c r="F13" s="68"/>
@@ -4577,8 +4350,8 @@
       <c r="C14" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="177"/>
-      <c r="E14" s="177"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="197"/>
       <c r="F14" s="113" t="s">
         <v>69</v>
       </c>
@@ -4588,12 +4361,12 @@
       <c r="H14" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="178" t="s">
+      <c r="I14" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="J14" s="179"/>
-      <c r="K14" s="179"/>
-      <c r="L14" s="180"/>
+      <c r="J14" s="199"/>
+      <c r="K14" s="199"/>
+      <c r="L14" s="200"/>
       <c r="M14" s="103" t="s">
         <v>41</v>
       </c>
@@ -4601,1062 +4374,702 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="2:14" s="197" customFormat="1" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="191">
+    <row r="15" spans="2:14" s="120" customFormat="1" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="114">
         <v>1</v>
       </c>
-      <c r="C15" s="192">
-        <v>46242</v>
-      </c>
-      <c r="D15" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="193" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="193" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" s="194" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="203" t="s">
-        <v>141</v>
-      </c>
-      <c r="J15" s="203"/>
-      <c r="K15" s="203"/>
-      <c r="L15" s="203"/>
-      <c r="M15" s="196">
-        <v>380</v>
-      </c>
-      <c r="N15" s="196">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="198">
+      <c r="C15" s="115"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="188"/>
+      <c r="J15" s="188"/>
+      <c r="K15" s="188"/>
+      <c r="L15" s="188"/>
+      <c r="M15" s="119">
+        <v>0</v>
+      </c>
+      <c r="N15" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="121">
         <f t="shared" ref="B16:B50" si="0">+B15+1</f>
         <v>2</v>
       </c>
-      <c r="C16" s="192">
-        <v>46242</v>
-      </c>
-      <c r="D16" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" s="193" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="193" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" s="194" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I16" s="203" t="s">
-        <v>142</v>
-      </c>
-      <c r="J16" s="203"/>
-      <c r="K16" s="203"/>
-      <c r="L16" s="203"/>
-      <c r="M16" s="196">
-        <v>0</v>
-      </c>
-      <c r="N16" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" s="197" customFormat="1" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="198">
+      <c r="C16" s="115"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="188"/>
+      <c r="J16" s="188"/>
+      <c r="K16" s="188"/>
+      <c r="L16" s="188"/>
+      <c r="M16" s="119">
+        <v>0</v>
+      </c>
+      <c r="N16" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" s="120" customFormat="1" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="121">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C17" s="192">
-        <v>46243</v>
-      </c>
-      <c r="D17" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" s="193" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="193" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="194" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I17" s="203" t="s">
-        <v>143</v>
-      </c>
-      <c r="J17" s="203"/>
-      <c r="K17" s="203"/>
-      <c r="L17" s="203"/>
-      <c r="M17" s="196">
-        <v>0</v>
-      </c>
-      <c r="N17" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="198">
+      <c r="C17" s="115"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="188"/>
+      <c r="J17" s="188"/>
+      <c r="K17" s="188"/>
+      <c r="L17" s="188"/>
+      <c r="M17" s="119">
+        <v>0</v>
+      </c>
+      <c r="N17" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="121">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C18" s="192">
-        <v>46243</v>
-      </c>
-      <c r="D18" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="193" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" s="193" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="194" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I18" s="203" t="s">
-        <v>144</v>
-      </c>
-      <c r="J18" s="203"/>
-      <c r="K18" s="203"/>
-      <c r="L18" s="203"/>
-      <c r="M18" s="196">
-        <v>0</v>
-      </c>
-      <c r="N18" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" s="197" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="198">
+      <c r="C18" s="115"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="188"/>
+      <c r="J18" s="188"/>
+      <c r="K18" s="188"/>
+      <c r="L18" s="188"/>
+      <c r="M18" s="119">
+        <v>0</v>
+      </c>
+      <c r="N18" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" s="120" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="121">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C19" s="192">
-        <v>46243</v>
-      </c>
-      <c r="D19" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="193" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" s="193" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="194" t="s">
-        <v>120</v>
-      </c>
-      <c r="H19" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I19" s="203" t="s">
-        <v>145</v>
-      </c>
-      <c r="J19" s="203"/>
-      <c r="K19" s="203"/>
-      <c r="L19" s="203"/>
-      <c r="M19" s="196">
+      <c r="C19" s="115"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="188"/>
+      <c r="J19" s="188"/>
+      <c r="K19" s="188"/>
+      <c r="L19" s="188"/>
+      <c r="M19" s="119">
         <v>40</v>
       </c>
-      <c r="N19" s="196">
+      <c r="N19" s="119">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="2:14" s="197" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="198">
+    <row r="20" spans="2:14" s="120" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="121">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C20" s="192">
-        <v>46243</v>
-      </c>
-      <c r="D20" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="193" t="s">
-        <v>104</v>
-      </c>
-      <c r="F20" s="193" t="s">
-        <v>107</v>
-      </c>
-      <c r="G20" s="194" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" s="203" t="s">
-        <v>145</v>
-      </c>
-      <c r="J20" s="203"/>
-      <c r="K20" s="203"/>
-      <c r="L20" s="203"/>
-      <c r="M20" s="196">
-        <v>0</v>
-      </c>
-      <c r="N20" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="198">
+      <c r="C20" s="115"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="188"/>
+      <c r="J20" s="188"/>
+      <c r="K20" s="188"/>
+      <c r="L20" s="188"/>
+      <c r="M20" s="119">
+        <v>0</v>
+      </c>
+      <c r="N20" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="121">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C21" s="192">
-        <v>46243</v>
-      </c>
-      <c r="D21" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" s="193" t="s">
-        <v>104</v>
-      </c>
-      <c r="F21" s="193" t="s">
-        <v>107</v>
-      </c>
-      <c r="G21" s="194" t="s">
-        <v>122</v>
-      </c>
-      <c r="H21" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" s="203" t="s">
-        <v>146</v>
-      </c>
-      <c r="J21" s="203"/>
-      <c r="K21" s="203"/>
-      <c r="L21" s="203"/>
-      <c r="M21" s="196">
-        <v>0</v>
-      </c>
-      <c r="N21" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" s="197" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="198">
+      <c r="C21" s="115"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="188"/>
+      <c r="J21" s="188"/>
+      <c r="K21" s="188"/>
+      <c r="L21" s="188"/>
+      <c r="M21" s="119">
+        <v>0</v>
+      </c>
+      <c r="N21" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" s="120" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="121">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C22" s="192">
-        <v>46243</v>
-      </c>
-      <c r="D22" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" s="193" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" s="193" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="194" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I22" s="203" t="s">
-        <v>147</v>
-      </c>
-      <c r="J22" s="203"/>
-      <c r="K22" s="203"/>
-      <c r="L22" s="203"/>
-      <c r="M22" s="196">
+      <c r="C22" s="115"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="188"/>
+      <c r="J22" s="188"/>
+      <c r="K22" s="188"/>
+      <c r="L22" s="188"/>
+      <c r="M22" s="119">
         <v>100</v>
       </c>
-      <c r="N22" s="196">
+      <c r="N22" s="119">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="198">
+    <row r="23" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="121">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C23" s="192">
-        <v>46243</v>
-      </c>
-      <c r="D23" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="193" t="s">
+      <c r="C23" s="115"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="188"/>
+      <c r="J23" s="188"/>
+      <c r="K23" s="188"/>
+      <c r="L23" s="188"/>
+      <c r="M23" s="119">
         <v>100</v>
       </c>
-      <c r="F23" s="193" t="s">
-        <v>101</v>
-      </c>
-      <c r="G23" s="199" t="s">
-        <v>124</v>
-      </c>
-      <c r="H23" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="203" t="s">
-        <v>148</v>
-      </c>
-      <c r="J23" s="203"/>
-      <c r="K23" s="203"/>
-      <c r="L23" s="203"/>
-      <c r="M23" s="196">
+      <c r="N23" s="119">
         <v>100</v>
       </c>
-      <c r="N23" s="196">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="198">
+    </row>
+    <row r="24" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="121">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C24" s="192">
-        <v>46243</v>
-      </c>
-      <c r="D24" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="193" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="193" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="200" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="203" t="s">
-        <v>149</v>
-      </c>
-      <c r="J24" s="203"/>
-      <c r="K24" s="203"/>
-      <c r="L24" s="203"/>
-      <c r="M24" s="196">
-        <v>0</v>
-      </c>
-      <c r="N24" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="198">
+      <c r="C24" s="115"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="116"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" s="188"/>
+      <c r="J24" s="188"/>
+      <c r="K24" s="188"/>
+      <c r="L24" s="188"/>
+      <c r="M24" s="119">
+        <v>0</v>
+      </c>
+      <c r="N24" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="121">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C25" s="192">
-        <v>46244</v>
-      </c>
-      <c r="D25" s="193" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="193" t="s">
-        <v>114</v>
-      </c>
-      <c r="F25" s="193" t="s">
-        <v>115</v>
-      </c>
-      <c r="G25" s="194" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="203" t="s">
-        <v>150</v>
-      </c>
-      <c r="J25" s="203"/>
-      <c r="K25" s="203"/>
-      <c r="L25" s="203"/>
-      <c r="M25" s="196">
-        <v>0</v>
-      </c>
-      <c r="N25" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" s="197" customFormat="1" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="198">
+      <c r="C25" s="115"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="116"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="188"/>
+      <c r="J25" s="188"/>
+      <c r="K25" s="188"/>
+      <c r="L25" s="188"/>
+      <c r="M25" s="119">
+        <v>0</v>
+      </c>
+      <c r="N25" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" s="120" customFormat="1" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="121">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C26" s="192">
-        <v>46244</v>
-      </c>
-      <c r="D26" s="193" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" s="193" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" s="193" t="s">
-        <v>115</v>
-      </c>
-      <c r="G26" s="194" t="s">
-        <v>127</v>
-      </c>
-      <c r="H26" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I26" s="203" t="s">
-        <v>150</v>
-      </c>
-      <c r="J26" s="203"/>
-      <c r="K26" s="203"/>
-      <c r="L26" s="203"/>
-      <c r="M26" s="196">
-        <v>0</v>
-      </c>
-      <c r="N26" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="198">
+      <c r="C26" s="115"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="188"/>
+      <c r="J26" s="188"/>
+      <c r="K26" s="188"/>
+      <c r="L26" s="188"/>
+      <c r="M26" s="119">
+        <v>0</v>
+      </c>
+      <c r="N26" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="121">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C27" s="192">
-        <v>46244</v>
-      </c>
-      <c r="D27" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" s="193" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="193" t="s">
-        <v>106</v>
-      </c>
-      <c r="G27" s="194" t="s">
-        <v>128</v>
-      </c>
-      <c r="H27" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I27" s="203" t="s">
-        <v>151</v>
-      </c>
-      <c r="J27" s="203"/>
-      <c r="K27" s="203"/>
-      <c r="L27" s="203"/>
-      <c r="M27" s="196">
-        <v>0</v>
-      </c>
-      <c r="N27" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="198">
+      <c r="C27" s="115"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="188"/>
+      <c r="J27" s="188"/>
+      <c r="K27" s="188"/>
+      <c r="L27" s="188"/>
+      <c r="M27" s="119">
+        <v>0</v>
+      </c>
+      <c r="N27" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="121">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C28" s="192">
-        <v>46245</v>
-      </c>
-      <c r="D28" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" s="193" t="s">
-        <v>98</v>
-      </c>
-      <c r="F28" s="193" t="s">
-        <v>99</v>
-      </c>
-      <c r="G28" s="194" t="s">
-        <v>129</v>
-      </c>
-      <c r="H28" s="195"/>
-      <c r="I28" s="203" t="s">
-        <v>152</v>
-      </c>
-      <c r="J28" s="203"/>
-      <c r="K28" s="203"/>
-      <c r="L28" s="203"/>
-      <c r="M28" s="196">
+      <c r="C28" s="115"/>
+      <c r="D28" s="116"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="188"/>
+      <c r="J28" s="188"/>
+      <c r="K28" s="188"/>
+      <c r="L28" s="188"/>
+      <c r="M28" s="119">
         <v>380</v>
       </c>
-      <c r="N28" s="196">
+      <c r="N28" s="119">
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="2:14" s="197" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="198">
+    <row r="29" spans="2:14" s="120" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="121">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C29" s="192">
-        <v>46245</v>
-      </c>
-      <c r="D29" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" s="193" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" s="193" t="s">
-        <v>99</v>
-      </c>
-      <c r="G29" s="194" t="s">
-        <v>119</v>
-      </c>
-      <c r="H29" s="195"/>
-      <c r="I29" s="203" t="s">
-        <v>153</v>
-      </c>
-      <c r="J29" s="203"/>
-      <c r="K29" s="203"/>
-      <c r="L29" s="203"/>
-      <c r="M29" s="196">
-        <v>0</v>
-      </c>
-      <c r="N29" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="198">
+      <c r="C29" s="115"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="116"/>
+      <c r="G29" s="117"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="188"/>
+      <c r="J29" s="188"/>
+      <c r="K29" s="188"/>
+      <c r="L29" s="188"/>
+      <c r="M29" s="119">
+        <v>0</v>
+      </c>
+      <c r="N29" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="121">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C30" s="192">
-        <v>46245</v>
-      </c>
-      <c r="D30" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="193" t="s">
-        <v>105</v>
-      </c>
-      <c r="F30" s="193" t="s">
-        <v>106</v>
-      </c>
-      <c r="G30" s="194" t="s">
-        <v>128</v>
-      </c>
-      <c r="H30" s="195"/>
-      <c r="I30" s="203" t="s">
-        <v>154</v>
-      </c>
-      <c r="J30" s="203"/>
-      <c r="K30" s="203"/>
-      <c r="L30" s="203"/>
-      <c r="M30" s="196">
+      <c r="C30" s="115"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="116"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="188"/>
+      <c r="J30" s="188"/>
+      <c r="K30" s="188"/>
+      <c r="L30" s="188"/>
+      <c r="M30" s="119">
         <v>40</v>
       </c>
-      <c r="N30" s="196">
+      <c r="N30" s="119">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:14" s="197" customFormat="1" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="198">
+    <row r="31" spans="2:14" s="120" customFormat="1" ht="90.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="121">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C31" s="192">
-        <v>46246</v>
-      </c>
-      <c r="D31" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="193" t="s">
-        <v>104</v>
-      </c>
-      <c r="F31" s="193" t="s">
-        <v>107</v>
-      </c>
-      <c r="G31" s="194" t="s">
-        <v>130</v>
-      </c>
-      <c r="H31" s="195"/>
-      <c r="I31" s="203" t="s">
-        <v>155</v>
-      </c>
-      <c r="J31" s="203"/>
-      <c r="K31" s="203"/>
-      <c r="L31" s="203"/>
-      <c r="M31" s="196">
+      <c r="C31" s="115"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="116"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="188"/>
+      <c r="J31" s="188"/>
+      <c r="K31" s="188"/>
+      <c r="L31" s="188"/>
+      <c r="M31" s="119">
         <v>40</v>
       </c>
-      <c r="N31" s="196">
+      <c r="N31" s="119">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="198">
+    <row r="32" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="121">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C32" s="192">
-        <v>46246</v>
-      </c>
-      <c r="D32" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32" s="193" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32" s="193" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="194" t="s">
-        <v>131</v>
-      </c>
-      <c r="H32" s="195"/>
-      <c r="I32" s="203" t="s">
-        <v>156</v>
-      </c>
-      <c r="J32" s="203"/>
-      <c r="K32" s="203"/>
-      <c r="L32" s="203"/>
-      <c r="M32" s="196">
+      <c r="C32" s="115"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="116"/>
+      <c r="F32" s="116"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="118"/>
+      <c r="I32" s="188"/>
+      <c r="J32" s="188"/>
+      <c r="K32" s="188"/>
+      <c r="L32" s="188"/>
+      <c r="M32" s="119">
         <v>160</v>
       </c>
-      <c r="N32" s="196">
+      <c r="N32" s="119">
         <v>160</v>
       </c>
     </row>
-    <row r="33" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="198">
+    <row r="33" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="121">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C33" s="192">
-        <v>46246</v>
-      </c>
-      <c r="D33" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E33" s="193" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="193" t="s">
-        <v>101</v>
-      </c>
-      <c r="G33" s="194" t="s">
-        <v>125</v>
-      </c>
-      <c r="H33" s="195"/>
-      <c r="I33" s="203" t="s">
-        <v>157</v>
-      </c>
-      <c r="J33" s="203"/>
-      <c r="K33" s="203"/>
-      <c r="L33" s="203"/>
-      <c r="M33" s="196">
-        <v>0</v>
-      </c>
-      <c r="N33" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="198">
+      <c r="C33" s="115"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="116"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="118"/>
+      <c r="I33" s="188"/>
+      <c r="J33" s="188"/>
+      <c r="K33" s="188"/>
+      <c r="L33" s="188"/>
+      <c r="M33" s="119">
+        <v>0</v>
+      </c>
+      <c r="N33" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="121">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C34" s="192">
-        <v>46246</v>
-      </c>
-      <c r="D34" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="193" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" s="193" t="s">
-        <v>103</v>
-      </c>
-      <c r="G34" s="194" t="s">
-        <v>132</v>
-      </c>
-      <c r="H34" s="195"/>
-      <c r="I34" s="203" t="s">
-        <v>158</v>
-      </c>
-      <c r="J34" s="203"/>
-      <c r="K34" s="203"/>
-      <c r="L34" s="203"/>
-      <c r="M34" s="196">
+      <c r="C34" s="115"/>
+      <c r="D34" s="116"/>
+      <c r="E34" s="116"/>
+      <c r="F34" s="116"/>
+      <c r="G34" s="117"/>
+      <c r="H34" s="118"/>
+      <c r="I34" s="188"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="188"/>
+      <c r="L34" s="188"/>
+      <c r="M34" s="119">
         <v>100</v>
       </c>
-      <c r="N34" s="196">
+      <c r="N34" s="119">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="2:14" s="197" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="198">
+    <row r="35" spans="2:14" s="120" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="121">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C35" s="192">
-        <v>46246</v>
-      </c>
-      <c r="D35" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" s="193" t="s">
-        <v>102</v>
-      </c>
-      <c r="F35" s="193" t="s">
-        <v>103</v>
-      </c>
-      <c r="G35" s="199" t="s">
-        <v>133</v>
-      </c>
-      <c r="H35" s="195"/>
-      <c r="I35" s="203" t="s">
-        <v>159</v>
-      </c>
-      <c r="J35" s="203"/>
-      <c r="K35" s="203"/>
-      <c r="L35" s="203"/>
-      <c r="M35" s="196">
-        <v>0</v>
-      </c>
-      <c r="N35" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:14" s="197" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="198">
+      <c r="C35" s="115"/>
+      <c r="D35" s="116"/>
+      <c r="E35" s="116"/>
+      <c r="F35" s="116"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="118"/>
+      <c r="I35" s="188"/>
+      <c r="J35" s="188"/>
+      <c r="K35" s="188"/>
+      <c r="L35" s="188"/>
+      <c r="M35" s="119">
+        <v>0</v>
+      </c>
+      <c r="N35" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" s="120" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="121">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C36" s="192">
-        <v>46246</v>
-      </c>
-      <c r="D36" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E36" s="193" t="s">
-        <v>102</v>
-      </c>
-      <c r="F36" s="193" t="s">
-        <v>103</v>
-      </c>
-      <c r="G36" s="199" t="s">
-        <v>134</v>
-      </c>
-      <c r="H36" s="195"/>
-      <c r="I36" s="203" t="s">
-        <v>160</v>
-      </c>
-      <c r="J36" s="203"/>
-      <c r="K36" s="203"/>
-      <c r="L36" s="203"/>
-      <c r="M36" s="196">
-        <v>0</v>
-      </c>
-      <c r="N36" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14" s="197" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="198">
+      <c r="C36" s="115"/>
+      <c r="D36" s="116"/>
+      <c r="E36" s="116"/>
+      <c r="F36" s="116"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="188"/>
+      <c r="J36" s="188"/>
+      <c r="K36" s="188"/>
+      <c r="L36" s="188"/>
+      <c r="M36" s="119">
+        <v>0</v>
+      </c>
+      <c r="N36" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" s="120" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="121">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C37" s="192">
-        <v>46246</v>
-      </c>
-      <c r="D37" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" s="193" t="s">
-        <v>102</v>
-      </c>
-      <c r="F37" s="193" t="s">
-        <v>103</v>
-      </c>
-      <c r="G37" s="200" t="s">
-        <v>135</v>
-      </c>
-      <c r="H37" s="195"/>
-      <c r="I37" s="203" t="s">
-        <v>161</v>
-      </c>
-      <c r="J37" s="203"/>
-      <c r="K37" s="203"/>
-      <c r="L37" s="203"/>
-      <c r="M37" s="196">
-        <v>0</v>
-      </c>
-      <c r="N37" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="198">
+      <c r="C37" s="115"/>
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="116"/>
+      <c r="G37" s="123"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="188"/>
+      <c r="J37" s="188"/>
+      <c r="K37" s="188"/>
+      <c r="L37" s="188"/>
+      <c r="M37" s="119">
+        <v>0</v>
+      </c>
+      <c r="N37" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="121">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C38" s="192">
-        <v>46246</v>
-      </c>
-      <c r="D38" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E38" s="193" t="s">
-        <v>102</v>
-      </c>
-      <c r="F38" s="193" t="s">
-        <v>103</v>
-      </c>
-      <c r="G38" s="199" t="s">
-        <v>111</v>
-      </c>
-      <c r="H38" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I38" s="203" t="s">
-        <v>162</v>
-      </c>
-      <c r="J38" s="203"/>
-      <c r="K38" s="203"/>
-      <c r="L38" s="203"/>
-      <c r="M38" s="196">
-        <v>0</v>
-      </c>
-      <c r="N38" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" s="197" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="198">
+      <c r="C38" s="115"/>
+      <c r="D38" s="116"/>
+      <c r="E38" s="116"/>
+      <c r="F38" s="116"/>
+      <c r="G38" s="122"/>
+      <c r="H38" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="188"/>
+      <c r="J38" s="188"/>
+      <c r="K38" s="188"/>
+      <c r="L38" s="188"/>
+      <c r="M38" s="119">
+        <v>0</v>
+      </c>
+      <c r="N38" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" s="120" customFormat="1" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="121">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C39" s="192">
-        <v>46247</v>
-      </c>
-      <c r="D39" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E39" s="193" t="s">
-        <v>104</v>
-      </c>
-      <c r="F39" s="193" t="s">
-        <v>108</v>
-      </c>
-      <c r="G39" s="201" t="s">
-        <v>136</v>
-      </c>
-      <c r="H39" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I39" s="203" t="s">
-        <v>163</v>
-      </c>
-      <c r="J39" s="203"/>
-      <c r="K39" s="203"/>
-      <c r="L39" s="203"/>
-      <c r="M39" s="196">
+      <c r="C39" s="115"/>
+      <c r="D39" s="116"/>
+      <c r="E39" s="116"/>
+      <c r="F39" s="116"/>
+      <c r="G39" s="124"/>
+      <c r="H39" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="188"/>
+      <c r="J39" s="188"/>
+      <c r="K39" s="188"/>
+      <c r="L39" s="188"/>
+      <c r="M39" s="119">
         <v>40</v>
       </c>
-      <c r="N39" s="196">
+      <c r="N39" s="119">
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="2:14" s="197" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="198">
+    <row r="40" spans="2:14" s="120" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="121">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C40" s="192">
-        <v>46247</v>
-      </c>
-      <c r="D40" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E40" s="193" t="s">
-        <v>104</v>
-      </c>
-      <c r="F40" s="193" t="s">
-        <v>107</v>
-      </c>
-      <c r="G40" s="201" t="s">
-        <v>137</v>
-      </c>
-      <c r="H40" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I40" s="203" t="s">
-        <v>164</v>
-      </c>
-      <c r="J40" s="203"/>
-      <c r="K40" s="203"/>
-      <c r="L40" s="203"/>
-      <c r="M40" s="196">
+      <c r="C40" s="115"/>
+      <c r="D40" s="116"/>
+      <c r="E40" s="116"/>
+      <c r="F40" s="116"/>
+      <c r="G40" s="124"/>
+      <c r="H40" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I40" s="188"/>
+      <c r="J40" s="188"/>
+      <c r="K40" s="188"/>
+      <c r="L40" s="188"/>
+      <c r="M40" s="119">
         <v>40</v>
       </c>
-      <c r="N40" s="196">
+      <c r="N40" s="119">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="2:14" s="197" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="198">
+    <row r="41" spans="2:14" s="120" customFormat="1" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="121">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C41" s="192">
-        <v>46247</v>
-      </c>
-      <c r="D41" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E41" s="193" t="s">
-        <v>98</v>
-      </c>
-      <c r="F41" s="193" t="s">
-        <v>99</v>
-      </c>
-      <c r="G41" s="201" t="s">
-        <v>138</v>
-      </c>
-      <c r="H41" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I41" s="203" t="s">
-        <v>165</v>
-      </c>
-      <c r="J41" s="203"/>
-      <c r="K41" s="203"/>
-      <c r="L41" s="203"/>
-      <c r="M41" s="196">
-        <v>0</v>
-      </c>
-      <c r="N41" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" s="197" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="202">
+      <c r="C41" s="115"/>
+      <c r="D41" s="116"/>
+      <c r="E41" s="116"/>
+      <c r="F41" s="116"/>
+      <c r="G41" s="124"/>
+      <c r="H41" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" s="188"/>
+      <c r="J41" s="188"/>
+      <c r="K41" s="188"/>
+      <c r="L41" s="188"/>
+      <c r="M41" s="119">
+        <v>0</v>
+      </c>
+      <c r="N41" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" s="120" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="125">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C42" s="192">
-        <v>46247</v>
-      </c>
-      <c r="D42" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E42" s="193" t="s">
-        <v>104</v>
-      </c>
-      <c r="F42" s="193" t="s">
-        <v>107</v>
-      </c>
-      <c r="G42" s="201" t="s">
-        <v>139</v>
-      </c>
-      <c r="H42" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I42" s="203" t="s">
-        <v>166</v>
-      </c>
-      <c r="J42" s="203"/>
-      <c r="K42" s="203"/>
-      <c r="L42" s="203"/>
-      <c r="M42" s="196">
-        <v>0</v>
-      </c>
-      <c r="N42" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" s="197" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="198">
+      <c r="C42" s="115"/>
+      <c r="D42" s="116"/>
+      <c r="E42" s="116"/>
+      <c r="F42" s="116"/>
+      <c r="G42" s="124"/>
+      <c r="H42" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I42" s="188"/>
+      <c r="J42" s="188"/>
+      <c r="K42" s="188"/>
+      <c r="L42" s="188"/>
+      <c r="M42" s="119">
+        <v>0</v>
+      </c>
+      <c r="N42" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" s="120" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="121">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C43" s="192">
-        <v>46247</v>
-      </c>
-      <c r="D43" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E43" s="193" t="s">
-        <v>104</v>
-      </c>
-      <c r="F43" s="193" t="s">
-        <v>107</v>
-      </c>
-      <c r="G43" s="201" t="s">
-        <v>140</v>
-      </c>
-      <c r="H43" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I43" s="203" t="s">
-        <v>167</v>
-      </c>
-      <c r="J43" s="203"/>
-      <c r="K43" s="203"/>
-      <c r="L43" s="203"/>
-      <c r="M43" s="196">
-        <v>0</v>
-      </c>
-      <c r="N43" s="196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" s="197" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="202">
+      <c r="C43" s="115"/>
+      <c r="D43" s="116"/>
+      <c r="E43" s="116"/>
+      <c r="F43" s="116"/>
+      <c r="G43" s="124"/>
+      <c r="H43" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I43" s="188"/>
+      <c r="J43" s="188"/>
+      <c r="K43" s="188"/>
+      <c r="L43" s="188"/>
+      <c r="M43" s="119">
+        <v>0</v>
+      </c>
+      <c r="N43" s="119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" s="120" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="125">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C44" s="192">
-        <v>46247</v>
-      </c>
-      <c r="D44" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="E44" s="193" t="s">
-        <v>109</v>
-      </c>
-      <c r="F44" s="193" t="s">
-        <v>110</v>
-      </c>
-      <c r="G44" s="201" t="s">
-        <v>112</v>
-      </c>
-      <c r="H44" s="195" t="s">
-        <v>94</v>
-      </c>
-      <c r="I44" s="203" t="s">
-        <v>168</v>
-      </c>
-      <c r="J44" s="203"/>
-      <c r="K44" s="203"/>
-      <c r="L44" s="203"/>
-      <c r="M44" s="196">
+      <c r="C44" s="115"/>
+      <c r="D44" s="116"/>
+      <c r="E44" s="116"/>
+      <c r="F44" s="116"/>
+      <c r="G44" s="124"/>
+      <c r="H44" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="I44" s="188"/>
+      <c r="J44" s="188"/>
+      <c r="K44" s="188"/>
+      <c r="L44" s="188"/>
+      <c r="M44" s="119">
         <v>80</v>
       </c>
-      <c r="N44" s="196">
+      <c r="N44" s="119">
         <v>80</v>
       </c>
     </row>
@@ -5665,30 +5078,18 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C45" s="110">
-        <v>46248</v>
-      </c>
-      <c r="D45" s="100" t="s">
-        <v>97</v>
-      </c>
-      <c r="E45" s="100" t="s">
-        <v>109</v>
-      </c>
-      <c r="F45" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="G45" s="112" t="s">
-        <v>169</v>
-      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="100"/>
+      <c r="E45" s="100"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="112"/>
       <c r="H45" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="I45" s="183" t="s">
-        <v>171</v>
-      </c>
-      <c r="J45" s="183"/>
-      <c r="K45" s="183"/>
-      <c r="L45" s="183"/>
+        <v>93</v>
+      </c>
+      <c r="I45" s="203"/>
+      <c r="J45" s="203"/>
+      <c r="K45" s="203"/>
+      <c r="L45" s="203"/>
       <c r="M45" s="111">
         <v>80</v>
       </c>
@@ -5701,30 +5102,18 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C46" s="110">
-        <v>46248</v>
-      </c>
-      <c r="D46" s="100" t="s">
-        <v>97</v>
-      </c>
-      <c r="E46" s="100" t="s">
-        <v>102</v>
-      </c>
-      <c r="F46" s="100" t="s">
-        <v>103</v>
-      </c>
-      <c r="G46" s="112" t="s">
-        <v>170</v>
-      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="100"/>
+      <c r="E46" s="100"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="112"/>
       <c r="H46" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="I46" s="183" t="s">
-        <v>172</v>
-      </c>
-      <c r="J46" s="183"/>
-      <c r="K46" s="183"/>
-      <c r="L46" s="183"/>
+        <v>93</v>
+      </c>
+      <c r="I46" s="203"/>
+      <c r="J46" s="203"/>
+      <c r="K46" s="203"/>
+      <c r="L46" s="203"/>
       <c r="M46" s="111">
         <v>120</v>
       </c>
@@ -5743,12 +5132,12 @@
       <c r="F47" s="107"/>
       <c r="G47" s="101"/>
       <c r="H47" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="I47" s="183"/>
-      <c r="J47" s="183"/>
-      <c r="K47" s="183"/>
-      <c r="L47" s="183"/>
+        <v>93</v>
+      </c>
+      <c r="I47" s="203"/>
+      <c r="J47" s="203"/>
+      <c r="K47" s="203"/>
+      <c r="L47" s="203"/>
       <c r="M47" s="111"/>
       <c r="N47" s="102"/>
     </row>
@@ -5763,12 +5152,12 @@
       <c r="F48" s="107"/>
       <c r="G48" s="101"/>
       <c r="H48" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="I48" s="183"/>
-      <c r="J48" s="183"/>
-      <c r="K48" s="183"/>
-      <c r="L48" s="183"/>
+        <v>93</v>
+      </c>
+      <c r="I48" s="203"/>
+      <c r="J48" s="203"/>
+      <c r="K48" s="203"/>
+      <c r="L48" s="203"/>
       <c r="M48" s="111"/>
       <c r="N48" s="102"/>
     </row>
@@ -5783,12 +5172,12 @@
       <c r="F49" s="99"/>
       <c r="G49" s="99"/>
       <c r="H49" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="I49" s="189"/>
-      <c r="J49" s="189"/>
-      <c r="K49" s="189"/>
-      <c r="L49" s="189"/>
+        <v>93</v>
+      </c>
+      <c r="I49" s="194"/>
+      <c r="J49" s="194"/>
+      <c r="K49" s="194"/>
+      <c r="L49" s="194"/>
       <c r="M49" s="111"/>
       <c r="N49" s="109"/>
     </row>
@@ -5803,12 +5192,12 @@
       <c r="F50" s="99"/>
       <c r="G50" s="99"/>
       <c r="H50" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="I50" s="189"/>
-      <c r="J50" s="189"/>
-      <c r="K50" s="189"/>
-      <c r="L50" s="189"/>
+        <v>93</v>
+      </c>
+      <c r="I50" s="194"/>
+      <c r="J50" s="194"/>
+      <c r="K50" s="194"/>
+      <c r="L50" s="194"/>
       <c r="M50" s="111"/>
       <c r="N50" s="109"/>
     </row>
@@ -5849,81 +5238,81 @@
       <c r="D52" s="31"/>
     </row>
     <row r="53" spans="2:14" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="184" t="s">
+      <c r="B53" s="189" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="184"/>
-      <c r="D53" s="184"/>
-      <c r="E53" s="184"/>
-      <c r="F53" s="184"/>
-      <c r="G53" s="184"/>
-      <c r="H53" s="184"/>
-      <c r="I53" s="188" t="s">
+      <c r="C53" s="189"/>
+      <c r="D53" s="189"/>
+      <c r="E53" s="189"/>
+      <c r="F53" s="189"/>
+      <c r="G53" s="189"/>
+      <c r="H53" s="189"/>
+      <c r="I53" s="193" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="188"/>
-      <c r="K53" s="188"/>
-      <c r="L53" s="188"/>
+      <c r="J53" s="193"/>
+      <c r="K53" s="193"/>
+      <c r="L53" s="193"/>
       <c r="M53" s="66"/>
       <c r="N53" s="67"/>
     </row>
     <row r="54" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="184"/>
-      <c r="C54" s="184"/>
-      <c r="D54" s="184"/>
-      <c r="E54" s="184"/>
-      <c r="F54" s="184"/>
-      <c r="G54" s="184"/>
-      <c r="H54" s="184"/>
-      <c r="I54" s="190" t="s">
+      <c r="B54" s="189"/>
+      <c r="C54" s="189"/>
+      <c r="D54" s="189"/>
+      <c r="E54" s="189"/>
+      <c r="F54" s="189"/>
+      <c r="G54" s="189"/>
+      <c r="H54" s="189"/>
+      <c r="I54" s="195" t="s">
         <v>84</v>
       </c>
-      <c r="J54" s="190"/>
-      <c r="K54" s="190"/>
-      <c r="L54" s="190"/>
+      <c r="J54" s="195"/>
+      <c r="K54" s="195"/>
+      <c r="L54" s="195"/>
       <c r="M54" s="47">
         <f>SUM(M15:M53)</f>
-        <v>1700</v>
-      </c>
-      <c r="N54" s="181"/>
+        <v>1320</v>
+      </c>
+      <c r="N54" s="201"/>
     </row>
     <row r="55" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="184"/>
-      <c r="C55" s="184"/>
-      <c r="D55" s="184"/>
-      <c r="E55" s="184"/>
-      <c r="F55" s="184"/>
-      <c r="G55" s="184"/>
-      <c r="H55" s="184"/>
-      <c r="I55" s="190" t="s">
+      <c r="B55" s="189"/>
+      <c r="C55" s="189"/>
+      <c r="D55" s="189"/>
+      <c r="E55" s="189"/>
+      <c r="F55" s="189"/>
+      <c r="G55" s="189"/>
+      <c r="H55" s="189"/>
+      <c r="I55" s="195" t="s">
         <v>85</v>
       </c>
-      <c r="J55" s="190"/>
-      <c r="K55" s="190"/>
-      <c r="L55" s="190"/>
+      <c r="J55" s="195"/>
+      <c r="K55" s="195"/>
+      <c r="L55" s="195"/>
       <c r="M55" s="47">
         <v>0.25</v>
       </c>
-      <c r="N55" s="182"/>
+      <c r="N55" s="202"/>
     </row>
     <row r="56" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="184"/>
-      <c r="C56" s="184"/>
-      <c r="D56" s="184"/>
-      <c r="E56" s="184"/>
-      <c r="F56" s="184"/>
-      <c r="G56" s="184"/>
-      <c r="H56" s="184"/>
-      <c r="I56" s="190" t="s">
+      <c r="B56" s="189"/>
+      <c r="C56" s="189"/>
+      <c r="D56" s="189"/>
+      <c r="E56" s="189"/>
+      <c r="F56" s="189"/>
+      <c r="G56" s="189"/>
+      <c r="H56" s="189"/>
+      <c r="I56" s="195" t="s">
         <v>80</v>
       </c>
-      <c r="J56" s="190"/>
-      <c r="K56" s="190"/>
-      <c r="L56" s="190"/>
+      <c r="J56" s="195"/>
+      <c r="K56" s="195"/>
+      <c r="L56" s="195"/>
       <c r="M56" s="47"/>
       <c r="N56" s="48">
         <f>SUM(N15:N55)</f>
-        <v>1700</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="57" spans="2:14" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
@@ -5970,24 +5359,22 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="50">
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="N54:N55"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I33:L33"/>
     <mergeCell ref="B53:H56"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="D6:I6"/>
@@ -6004,22 +5391,24 @@
     <mergeCell ref="I18:L18"/>
     <mergeCell ref="I17:L17"/>
     <mergeCell ref="I16:L16"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="N54:N55"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backend/templates/plantilla-liquidacion.xlsx
+++ b/backend/templates/plantilla-liquidacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\seminario_2026\TechAssist\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB4552C-7622-455F-A647-BD140140F5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC18A8F-2863-4CAB-BC2D-831B915F9B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1735,6 +1735,151 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1762,9 +1907,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1792,149 +1934,31 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="3" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1958,30 +1982,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="3" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2116,67 +2116,6 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>809624</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>18354</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1476375</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FB6DAA0-1F31-827B-8AFA-7DDEDDCAC17F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="7051" t="28523" r="5128" b="46735"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1295399" y="12619929"/>
-          <a:ext cx="1704976" cy="896046"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2550,14 +2489,14 @@
     <row r="1" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="166" t="s">
+      <c r="C1" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
       <c r="I1" s="33"/>
       <c r="J1" s="50"/>
       <c r="K1" s="50"/>
@@ -2567,14 +2506,14 @@
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="34"/>
-      <c r="C2" s="167" t="s">
+      <c r="C2" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="167"/>
-      <c r="E2" s="167"/>
-      <c r="F2" s="167"/>
-      <c r="G2" s="167"/>
-      <c r="H2" s="167"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
       <c r="J2" s="52"/>
       <c r="K2" s="52"/>
       <c r="L2" s="52"/>
@@ -2597,12 +2536,12 @@
     <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="35"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
       <c r="I4" s="38"/>
       <c r="J4" s="38"/>
       <c r="K4" s="38"/>
@@ -2612,14 +2551,14 @@
     <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="35"/>
-      <c r="C5" s="133" t="s">
+      <c r="C5" s="178" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="178"/>
+      <c r="G5" s="178"/>
+      <c r="H5" s="178"/>
       <c r="I5" s="35"/>
       <c r="J5" s="38"/>
       <c r="K5" s="38"/>
@@ -2629,95 +2568,95 @@
     <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="35"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
+      <c r="C6" s="178"/>
+      <c r="D6" s="178"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="178"/>
       <c r="I6" s="35"/>
-      <c r="J6" s="127" t="s">
+      <c r="J6" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="127"/>
-      <c r="L6" s="128" t="s">
+      <c r="K6" s="172"/>
+      <c r="L6" s="173" t="s">
         <v>97</v>
       </c>
-      <c r="M6" s="129"/>
+      <c r="M6" s="174"/>
     </row>
     <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="35"/>
-      <c r="C7" s="132" t="s">
+      <c r="C7" s="177" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
+      <c r="D7" s="177"/>
+      <c r="E7" s="177"/>
+      <c r="F7" s="177"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="177"/>
       <c r="I7" s="35"/>
-      <c r="J7" s="127" t="s">
+      <c r="J7" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="127"/>
-      <c r="L7" s="130">
-        <v>0</v>
-      </c>
-      <c r="M7" s="131"/>
+      <c r="K7" s="172"/>
+      <c r="L7" s="175">
+        <v>0</v>
+      </c>
+      <c r="M7" s="176"/>
     </row>
     <row r="8" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
+      <c r="G8" s="177"/>
+      <c r="H8" s="177"/>
       <c r="I8" s="35"/>
-      <c r="J8" s="164" t="s">
+      <c r="J8" s="126" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="164"/>
-      <c r="L8" s="164"/>
-      <c r="M8" s="165"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="127"/>
     </row>
     <row r="9" spans="1:13" s="31" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="176" t="s">
+      <c r="A9" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="177"/>
-      <c r="C9" s="177"/>
-      <c r="D9" s="177"/>
-      <c r="E9" s="177"/>
-      <c r="F9" s="178" t="s">
+      <c r="B9" s="139"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="139"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="G9" s="179"/>
-      <c r="H9" s="179"/>
-      <c r="I9" s="179"/>
-      <c r="J9" s="179"/>
-      <c r="K9" s="179"/>
-      <c r="L9" s="180"/>
-      <c r="M9" s="181" t="s">
+      <c r="G9" s="141"/>
+      <c r="H9" s="141"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="142"/>
+      <c r="M9" s="143" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="184" t="s">
+      <c r="A10" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="184" t="s">
+      <c r="B10" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="184" t="s">
+      <c r="C10" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="184" t="s">
+      <c r="D10" s="146" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="186" t="s">
+      <c r="E10" s="148" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="74" t="s">
@@ -2741,14 +2680,14 @@
       <c r="L10" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="M10" s="182"/>
+      <c r="M10" s="144"/>
     </row>
     <row r="11" spans="1:13" s="8" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="185"/>
-      <c r="B11" s="185"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="187"/>
+      <c r="A11" s="147"/>
+      <c r="B11" s="147"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="149"/>
       <c r="F11" s="75">
         <v>46242</v>
       </c>
@@ -2776,7 +2715,7 @@
         <f t="shared" si="0"/>
         <v>46248</v>
       </c>
-      <c r="M11" s="183"/>
+      <c r="M11" s="145"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
@@ -3259,31 +3198,31 @@
         <f>(+E26+E25+E22+E21+E17+E15+E14+E13+E12+E19+E27+E18+E23+E24)*0.12</f>
         <v>0</v>
       </c>
-      <c r="F28" s="173"/>
-      <c r="G28" s="174"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="174"/>
-      <c r="K28" s="174"/>
-      <c r="L28" s="174"/>
-      <c r="M28" s="175"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="136"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="137"/>
     </row>
     <row r="29" spans="1:14" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="168" t="s">
+      <c r="A29" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="169"/>
-      <c r="C29" s="169"/>
-      <c r="D29" s="169"/>
-      <c r="E29" s="169"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="171"/>
-      <c r="I29" s="171"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="171"/>
-      <c r="L29" s="171"/>
-      <c r="M29" s="172"/>
+      <c r="B29" s="131"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="133"/>
+      <c r="I29" s="133"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="133"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="134"/>
       <c r="N29" s="16"/>
     </row>
     <row r="30" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -3754,10 +3693,10 @@
       <c r="N45" s="3"/>
     </row>
     <row r="46" spans="1:14" s="7" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="153"/>
-      <c r="B46" s="154"/>
-      <c r="C46" s="154"/>
-      <c r="D46" s="155"/>
+      <c r="A46" s="160"/>
+      <c r="B46" s="161"/>
+      <c r="C46" s="161"/>
+      <c r="D46" s="162"/>
       <c r="E46" s="63">
         <f>+E12+E13+E14+E15+E16+E17+E19+E20+E21+E22+E25+E26+E28+E30+E31+E32+E33+E34+E35+E41+E42+E43+E44+E45+E23+E24+E27+E36+E40+E37+E38+E39+E18</f>
         <v>0</v>
@@ -3797,102 +3736,102 @@
       <c r="N46" s="3"/>
     </row>
     <row r="47" spans="1:14" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A47" s="156" t="s">
+      <c r="A47" s="163" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="157"/>
-      <c r="C47" s="160"/>
-      <c r="D47" s="160"/>
-      <c r="E47" s="160"/>
-      <c r="F47" s="160"/>
-      <c r="G47" s="160"/>
-      <c r="H47" s="160"/>
-      <c r="I47" s="160"/>
-      <c r="J47" s="160"/>
-      <c r="K47" s="160"/>
-      <c r="L47" s="160"/>
-      <c r="M47" s="161"/>
+      <c r="B47" s="164"/>
+      <c r="C47" s="167"/>
+      <c r="D47" s="167"/>
+      <c r="E47" s="167"/>
+      <c r="F47" s="167"/>
+      <c r="G47" s="167"/>
+      <c r="H47" s="167"/>
+      <c r="I47" s="167"/>
+      <c r="J47" s="167"/>
+      <c r="K47" s="167"/>
+      <c r="L47" s="167"/>
+      <c r="M47" s="168"/>
       <c r="N47" s="3"/>
     </row>
     <row r="48" spans="1:14" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="158"/>
-      <c r="B48" s="159"/>
-      <c r="C48" s="162"/>
-      <c r="D48" s="162"/>
-      <c r="E48" s="162"/>
-      <c r="F48" s="162"/>
-      <c r="G48" s="162"/>
-      <c r="H48" s="162"/>
-      <c r="I48" s="162"/>
-      <c r="J48" s="162"/>
-      <c r="K48" s="162"/>
-      <c r="L48" s="162"/>
-      <c r="M48" s="163"/>
+      <c r="A48" s="165"/>
+      <c r="B48" s="166"/>
+      <c r="C48" s="169"/>
+      <c r="D48" s="169"/>
+      <c r="E48" s="169"/>
+      <c r="F48" s="169"/>
+      <c r="G48" s="169"/>
+      <c r="H48" s="169"/>
+      <c r="I48" s="169"/>
+      <c r="J48" s="169"/>
+      <c r="K48" s="169"/>
+      <c r="L48" s="169"/>
+      <c r="M48" s="170"/>
     </row>
     <row r="49" spans="1:13" s="7" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="144" t="s">
+      <c r="A49" s="151" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="145"/>
-      <c r="C49" s="145"/>
-      <c r="D49" s="145"/>
-      <c r="E49" s="145"/>
-      <c r="F49" s="145"/>
-      <c r="G49" s="145"/>
-      <c r="H49" s="145"/>
-      <c r="I49" s="145"/>
-      <c r="J49" s="145"/>
-      <c r="K49" s="145"/>
-      <c r="L49" s="145"/>
-      <c r="M49" s="146"/>
+      <c r="B49" s="152"/>
+      <c r="C49" s="152"/>
+      <c r="D49" s="152"/>
+      <c r="E49" s="152"/>
+      <c r="F49" s="152"/>
+      <c r="G49" s="152"/>
+      <c r="H49" s="152"/>
+      <c r="I49" s="152"/>
+      <c r="J49" s="152"/>
+      <c r="K49" s="152"/>
+      <c r="L49" s="152"/>
+      <c r="M49" s="153"/>
     </row>
     <row r="50" spans="1:13" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="147" t="str">
+      <c r="A50" s="154" t="str">
         <f>+CONCATENATE(KILOMETRAJE!F15," ",KILOMETRAJE!G15," ",KILOMETRAJE!F16," ",KILOMETRAJE!G16," ",KILOMETRAJE!F17," ",KILOMETRAJE!G17," ",KILOMETRAJE!F18," ",KILOMETRAJE!G18," ",KILOMETRAJE!F19," ",KILOMETRAJE!G19," ",KILOMETRAJE!F20," ",KILOMETRAJE!G20," ",KILOMETRAJE!F21," ",KILOMETRAJE!G21," ",KILOMETRAJE!F22," ",KILOMETRAJE!G22," ",KILOMETRAJE!F23," ",KILOMETRAJE!G23," ",KILOMETRAJE!F24," ",KILOMETRAJE!G24," ",KILOMETRAJE!F25," ",KILOMETRAJE!G25," ",KILOMETRAJE!F26," ",KILOMETRAJE!G26," ",KILOMETRAJE!F27," ",KILOMETRAJE!G27," ",KILOMETRAJE!F28," ",KILOMETRAJE!G28," ",KILOMETRAJE!F29," ",KILOMETRAJE!G29," ",KILOMETRAJE!F30," ",KILOMETRAJE!G30," ",KILOMETRAJE!F31," ",KILOMETRAJE!G31," ",KILOMETRAJE!F32," ",KILOMETRAJE!G32," ",KILOMETRAJE!F33," ",KILOMETRAJE!G33," ",KILOMETRAJE!F34," ",KILOMETRAJE!G34," ",KILOMETRAJE!F35," ",KILOMETRAJE!G35," ",KILOMETRAJE!F224," ",KILOMETRAJE!G36," ",KILOMETRAJE!F37," ",KILOMETRAJE!G37," ",KILOMETRAJE!F38," ",KILOMETRAJE!G38," ",KILOMETRAJE!F39," ",KILOMETRAJE!G39," ",KILOMETRAJE!F40," ",KILOMETRAJE!G40," ",KILOMETRAJE!F41," ",KILOMETRAJE!G41," ",KILOMETRAJE!F42," ",KILOMETRAJE!G42," ",KILOMETRAJE!F49," ",KILOMETRAJE!G49," ",KILOMETRAJE!F50," ",KILOMETRAJE!G50," ",)</f>
         <v xml:space="preserve">                                                            </v>
       </c>
-      <c r="B50" s="148"/>
-      <c r="C50" s="148"/>
-      <c r="D50" s="148"/>
-      <c r="E50" s="148"/>
-      <c r="F50" s="148"/>
-      <c r="G50" s="148"/>
-      <c r="H50" s="148"/>
-      <c r="I50" s="148"/>
-      <c r="J50" s="148"/>
-      <c r="K50" s="148"/>
-      <c r="L50" s="148"/>
-      <c r="M50" s="149"/>
+      <c r="B50" s="155"/>
+      <c r="C50" s="155"/>
+      <c r="D50" s="155"/>
+      <c r="E50" s="155"/>
+      <c r="F50" s="155"/>
+      <c r="G50" s="155"/>
+      <c r="H50" s="155"/>
+      <c r="I50" s="155"/>
+      <c r="J50" s="155"/>
+      <c r="K50" s="155"/>
+      <c r="L50" s="155"/>
+      <c r="M50" s="156"/>
     </row>
     <row r="51" spans="1:13" s="7" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="147"/>
-      <c r="B51" s="148"/>
-      <c r="C51" s="148"/>
-      <c r="D51" s="148"/>
-      <c r="E51" s="148"/>
-      <c r="F51" s="148"/>
-      <c r="G51" s="148"/>
-      <c r="H51" s="148"/>
-      <c r="I51" s="148"/>
-      <c r="J51" s="148"/>
-      <c r="K51" s="148"/>
-      <c r="L51" s="148"/>
-      <c r="M51" s="149"/>
+      <c r="A51" s="154"/>
+      <c r="B51" s="155"/>
+      <c r="C51" s="155"/>
+      <c r="D51" s="155"/>
+      <c r="E51" s="155"/>
+      <c r="F51" s="155"/>
+      <c r="G51" s="155"/>
+      <c r="H51" s="155"/>
+      <c r="I51" s="155"/>
+      <c r="J51" s="155"/>
+      <c r="K51" s="155"/>
+      <c r="L51" s="155"/>
+      <c r="M51" s="156"/>
     </row>
     <row r="52" spans="1:13" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="150"/>
-      <c r="B52" s="151"/>
-      <c r="C52" s="151"/>
-      <c r="D52" s="151"/>
-      <c r="E52" s="151"/>
-      <c r="F52" s="151"/>
-      <c r="G52" s="151"/>
-      <c r="H52" s="151"/>
-      <c r="I52" s="151"/>
-      <c r="J52" s="151"/>
-      <c r="K52" s="151"/>
-      <c r="L52" s="151"/>
-      <c r="M52" s="152"/>
+      <c r="A52" s="157"/>
+      <c r="B52" s="158"/>
+      <c r="C52" s="158"/>
+      <c r="D52" s="158"/>
+      <c r="E52" s="158"/>
+      <c r="F52" s="158"/>
+      <c r="G52" s="158"/>
+      <c r="H52" s="158"/>
+      <c r="I52" s="158"/>
+      <c r="J52" s="158"/>
+      <c r="K52" s="158"/>
+      <c r="L52" s="158"/>
+      <c r="M52" s="159"/>
     </row>
     <row r="53" spans="1:13" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="26"/>
@@ -3965,42 +3904,42 @@
       <c r="A58" s="30"/>
       <c r="B58" s="29"/>
       <c r="C58" s="22"/>
-      <c r="F58" s="134" t="s">
+      <c r="F58" s="150" t="s">
         <v>76</v>
       </c>
-      <c r="G58" s="134"/>
-      <c r="H58" s="134"/>
-      <c r="I58" s="134"/>
-      <c r="J58" s="134"/>
-      <c r="K58" s="134"/>
-      <c r="L58" s="134"/>
-      <c r="M58" s="134"/>
+      <c r="G58" s="150"/>
+      <c r="H58" s="150"/>
+      <c r="I58" s="150"/>
+      <c r="J58" s="150"/>
+      <c r="K58" s="150"/>
+      <c r="L58" s="150"/>
+      <c r="M58" s="150"/>
     </row>
     <row r="59" spans="1:13" s="7" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A59" s="30"/>
-      <c r="B59" s="139" t="str">
+      <c r="B59" s="183" t="str">
         <f>C5</f>
         <v>NOMBRE</v>
       </c>
-      <c r="C59" s="139"/>
-      <c r="F59" s="139" t="s">
+      <c r="C59" s="183"/>
+      <c r="F59" s="183" t="s">
         <v>77</v>
       </c>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="139"/>
-      <c r="L59" s="139"/>
-      <c r="M59" s="139"/>
+      <c r="G59" s="183"/>
+      <c r="H59" s="183"/>
+      <c r="I59" s="183"/>
+      <c r="J59" s="183"/>
+      <c r="K59" s="183"/>
+      <c r="L59" s="183"/>
+      <c r="M59" s="183"/>
     </row>
     <row r="60" spans="1:13" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="30"/>
-      <c r="B60" s="134" t="str">
+      <c r="B60" s="150" t="str">
         <f>C7</f>
         <v>CODIGO EMPLEADO</v>
       </c>
-      <c r="C60" s="134"/>
+      <c r="C60" s="150"/>
       <c r="F60" s="30"/>
       <c r="G60" s="30"/>
       <c r="H60" s="30"/>
@@ -4040,12 +3979,12 @@
       <c r="M63" s="7"/>
     </row>
     <row r="64" spans="1:13" ht="14.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="135" t="s">
+      <c r="B64" s="179" t="s">
         <v>46</v>
       </c>
-      <c r="C64" s="136"/>
-      <c r="D64" s="139"/>
-      <c r="E64" s="139"/>
+      <c r="C64" s="180"/>
+      <c r="D64" s="183"/>
+      <c r="E64" s="183"/>
       <c r="H64" s="30"/>
       <c r="I64" s="30"/>
       <c r="J64" s="30"/>
@@ -4054,10 +3993,10 @@
       <c r="M64" s="7"/>
     </row>
     <row r="65" spans="2:13" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="137"/>
-      <c r="C65" s="138"/>
-      <c r="D65" s="139"/>
-      <c r="E65" s="139"/>
+      <c r="B65" s="181"/>
+      <c r="C65" s="182"/>
+      <c r="D65" s="183"/>
+      <c r="E65" s="183"/>
       <c r="H65" s="30"/>
       <c r="I65" s="30"/>
       <c r="J65" s="30"/>
@@ -4066,37 +4005,37 @@
       <c r="M65" s="7"/>
     </row>
     <row r="66" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="140"/>
-      <c r="C66" s="141"/>
-      <c r="F66" s="134" t="s">
+      <c r="B66" s="184"/>
+      <c r="C66" s="185"/>
+      <c r="F66" s="150" t="s">
         <v>76</v>
       </c>
-      <c r="G66" s="134"/>
-      <c r="H66" s="134"/>
-      <c r="I66" s="134"/>
-      <c r="J66" s="134"/>
-      <c r="K66" s="134"/>
-      <c r="L66" s="134"/>
-      <c r="M66" s="134"/>
+      <c r="G66" s="150"/>
+      <c r="H66" s="150"/>
+      <c r="I66" s="150"/>
+      <c r="J66" s="150"/>
+      <c r="K66" s="150"/>
+      <c r="L66" s="150"/>
+      <c r="M66" s="150"/>
     </row>
     <row r="67" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="142"/>
-      <c r="C67" s="143"/>
-      <c r="H67" s="139" t="s">
+      <c r="B67" s="186"/>
+      <c r="C67" s="187"/>
+      <c r="H67" s="183" t="s">
         <v>45</v>
       </c>
-      <c r="I67" s="139"/>
-      <c r="J67" s="139"/>
-      <c r="K67" s="139"/>
+      <c r="I67" s="183"/>
+      <c r="J67" s="183"/>
+      <c r="K67" s="183"/>
       <c r="L67" s="41"/>
       <c r="M67" s="41"/>
     </row>
     <row r="68" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D68" s="126"/>
-      <c r="E68" s="126"/>
-      <c r="F68" s="126"/>
-      <c r="G68" s="126"/>
-      <c r="H68" s="126"/>
+      <c r="D68" s="171"/>
+      <c r="E68" s="171"/>
+      <c r="F68" s="171"/>
+      <c r="G68" s="171"/>
+      <c r="H68" s="171"/>
       <c r="I68" s="37"/>
       <c r="J68" s="37"/>
       <c r="K68" s="37"/>
@@ -4104,44 +4043,22 @@
       <c r="M68" s="37"/>
     </row>
     <row r="69" spans="2:13" ht="15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="126"/>
-      <c r="E69" s="126"/>
-      <c r="F69" s="126"/>
-      <c r="G69" s="126"/>
-      <c r="H69" s="126"/>
+      <c r="D69" s="171"/>
+      <c r="E69" s="171"/>
+      <c r="F69" s="171"/>
+      <c r="G69" s="171"/>
+      <c r="H69" s="171"/>
     </row>
     <row r="70" spans="2:13" ht="15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="126"/>
-      <c r="E70" s="126"/>
-      <c r="F70" s="126"/>
-      <c r="G70" s="126"/>
-      <c r="H70" s="126"/>
+      <c r="D70" s="171"/>
+      <c r="E70" s="171"/>
+      <c r="F70" s="171"/>
+      <c r="G70" s="171"/>
+      <c r="H70" s="171"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="38">
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="F29:M29"/>
-    <mergeCell ref="F28:M28"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F58:M58"/>
-    <mergeCell ref="A49:M49"/>
-    <mergeCell ref="A50:M52"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A47:B48"/>
-    <mergeCell ref="C47:M47"/>
-    <mergeCell ref="C48:M48"/>
     <mergeCell ref="D68:H70"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L6:M6"/>
@@ -4158,6 +4075,28 @@
     <mergeCell ref="H67:K67"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="F59:M59"/>
+    <mergeCell ref="F58:M58"/>
+    <mergeCell ref="A49:M49"/>
+    <mergeCell ref="A50:M52"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A47:B48"/>
+    <mergeCell ref="C47:M47"/>
+    <mergeCell ref="C48:M48"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="F29:M29"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
@@ -4201,14 +4140,14 @@
     <row r="5" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="167" t="s">
+      <c r="D5" s="129" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -4218,14 +4157,14 @@
     <row r="6" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="167" t="s">
+      <c r="D6" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="167"/>
-      <c r="I6" s="167"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -4250,12 +4189,12 @@
     <row r="8" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="190" t="s">
+      <c r="D8" s="198" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="190"/>
-      <c r="F8" s="190"/>
-      <c r="G8" s="190"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="198"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -4267,12 +4206,12 @@
     <row r="9" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="191" t="s">
+      <c r="D9" s="199" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="191"/>
-      <c r="F9" s="191"/>
-      <c r="G9" s="191"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="199"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -4284,12 +4223,12 @@
     <row r="10" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="192" t="s">
+      <c r="D10" s="200" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="192"/>
-      <c r="F10" s="192"/>
-      <c r="G10" s="192"/>
+      <c r="E10" s="200"/>
+      <c r="F10" s="200"/>
+      <c r="G10" s="200"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -4327,10 +4266,10 @@
     <row r="13" spans="2:14" s="31" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="68"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="196" t="s">
+      <c r="D13" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="196" t="s">
+      <c r="E13" s="188" t="s">
         <v>68</v>
       </c>
       <c r="F13" s="68"/>
@@ -4350,8 +4289,8 @@
       <c r="C14" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="197"/>
-      <c r="E14" s="197"/>
+      <c r="D14" s="189"/>
+      <c r="E14" s="189"/>
       <c r="F14" s="113" t="s">
         <v>69</v>
       </c>
@@ -4361,12 +4300,12 @@
       <c r="H14" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="198" t="s">
+      <c r="I14" s="190" t="s">
         <v>71</v>
       </c>
-      <c r="J14" s="199"/>
-      <c r="K14" s="199"/>
-      <c r="L14" s="200"/>
+      <c r="J14" s="191"/>
+      <c r="K14" s="191"/>
+      <c r="L14" s="192"/>
       <c r="M14" s="103" t="s">
         <v>41</v>
       </c>
@@ -4386,10 +4325,10 @@
       <c r="H15" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="188"/>
-      <c r="J15" s="188"/>
-      <c r="K15" s="188"/>
-      <c r="L15" s="188"/>
+      <c r="I15" s="195"/>
+      <c r="J15" s="195"/>
+      <c r="K15" s="195"/>
+      <c r="L15" s="195"/>
       <c r="M15" s="119">
         <v>0</v>
       </c>
@@ -4410,10 +4349,10 @@
       <c r="H16" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I16" s="188"/>
-      <c r="J16" s="188"/>
-      <c r="K16" s="188"/>
-      <c r="L16" s="188"/>
+      <c r="I16" s="195"/>
+      <c r="J16" s="195"/>
+      <c r="K16" s="195"/>
+      <c r="L16" s="195"/>
       <c r="M16" s="119">
         <v>0</v>
       </c>
@@ -4434,10 +4373,10 @@
       <c r="H17" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I17" s="188"/>
-      <c r="J17" s="188"/>
-      <c r="K17" s="188"/>
-      <c r="L17" s="188"/>
+      <c r="I17" s="195"/>
+      <c r="J17" s="195"/>
+      <c r="K17" s="195"/>
+      <c r="L17" s="195"/>
       <c r="M17" s="119">
         <v>0</v>
       </c>
@@ -4458,10 +4397,10 @@
       <c r="H18" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="188"/>
-      <c r="J18" s="188"/>
-      <c r="K18" s="188"/>
-      <c r="L18" s="188"/>
+      <c r="I18" s="195"/>
+      <c r="J18" s="195"/>
+      <c r="K18" s="195"/>
+      <c r="L18" s="195"/>
       <c r="M18" s="119">
         <v>0</v>
       </c>
@@ -4482,10 +4421,10 @@
       <c r="H19" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="188"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="188"/>
-      <c r="L19" s="188"/>
+      <c r="I19" s="195"/>
+      <c r="J19" s="195"/>
+      <c r="K19" s="195"/>
+      <c r="L19" s="195"/>
       <c r="M19" s="119">
         <v>40</v>
       </c>
@@ -4506,10 +4445,10 @@
       <c r="H20" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="188"/>
-      <c r="J20" s="188"/>
-      <c r="K20" s="188"/>
-      <c r="L20" s="188"/>
+      <c r="I20" s="195"/>
+      <c r="J20" s="195"/>
+      <c r="K20" s="195"/>
+      <c r="L20" s="195"/>
       <c r="M20" s="119">
         <v>0</v>
       </c>
@@ -4530,10 +4469,10 @@
       <c r="H21" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="188"/>
-      <c r="J21" s="188"/>
-      <c r="K21" s="188"/>
-      <c r="L21" s="188"/>
+      <c r="I21" s="195"/>
+      <c r="J21" s="195"/>
+      <c r="K21" s="195"/>
+      <c r="L21" s="195"/>
       <c r="M21" s="119">
         <v>0</v>
       </c>
@@ -4554,10 +4493,10 @@
       <c r="H22" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="188"/>
-      <c r="J22" s="188"/>
-      <c r="K22" s="188"/>
-      <c r="L22" s="188"/>
+      <c r="I22" s="195"/>
+      <c r="J22" s="195"/>
+      <c r="K22" s="195"/>
+      <c r="L22" s="195"/>
       <c r="M22" s="119">
         <v>100</v>
       </c>
@@ -4578,10 +4517,10 @@
       <c r="H23" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I23" s="188"/>
-      <c r="J23" s="188"/>
-      <c r="K23" s="188"/>
-      <c r="L23" s="188"/>
+      <c r="I23" s="195"/>
+      <c r="J23" s="195"/>
+      <c r="K23" s="195"/>
+      <c r="L23" s="195"/>
       <c r="M23" s="119">
         <v>100</v>
       </c>
@@ -4602,10 +4541,10 @@
       <c r="H24" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I24" s="188"/>
-      <c r="J24" s="188"/>
-      <c r="K24" s="188"/>
-      <c r="L24" s="188"/>
+      <c r="I24" s="195"/>
+      <c r="J24" s="195"/>
+      <c r="K24" s="195"/>
+      <c r="L24" s="195"/>
       <c r="M24" s="119">
         <v>0</v>
       </c>
@@ -4626,10 +4565,10 @@
       <c r="H25" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I25" s="188"/>
-      <c r="J25" s="188"/>
-      <c r="K25" s="188"/>
-      <c r="L25" s="188"/>
+      <c r="I25" s="195"/>
+      <c r="J25" s="195"/>
+      <c r="K25" s="195"/>
+      <c r="L25" s="195"/>
       <c r="M25" s="119">
         <v>0</v>
       </c>
@@ -4650,10 +4589,10 @@
       <c r="H26" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I26" s="188"/>
-      <c r="J26" s="188"/>
-      <c r="K26" s="188"/>
-      <c r="L26" s="188"/>
+      <c r="I26" s="195"/>
+      <c r="J26" s="195"/>
+      <c r="K26" s="195"/>
+      <c r="L26" s="195"/>
       <c r="M26" s="119">
         <v>0</v>
       </c>
@@ -4674,10 +4613,10 @@
       <c r="H27" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I27" s="188"/>
-      <c r="J27" s="188"/>
-      <c r="K27" s="188"/>
-      <c r="L27" s="188"/>
+      <c r="I27" s="195"/>
+      <c r="J27" s="195"/>
+      <c r="K27" s="195"/>
+      <c r="L27" s="195"/>
       <c r="M27" s="119">
         <v>0</v>
       </c>
@@ -4696,10 +4635,10 @@
       <c r="F28" s="116"/>
       <c r="G28" s="117"/>
       <c r="H28" s="118"/>
-      <c r="I28" s="188"/>
-      <c r="J28" s="188"/>
-      <c r="K28" s="188"/>
-      <c r="L28" s="188"/>
+      <c r="I28" s="195"/>
+      <c r="J28" s="195"/>
+      <c r="K28" s="195"/>
+      <c r="L28" s="195"/>
       <c r="M28" s="119">
         <v>380</v>
       </c>
@@ -4718,10 +4657,10 @@
       <c r="F29" s="116"/>
       <c r="G29" s="117"/>
       <c r="H29" s="118"/>
-      <c r="I29" s="188"/>
-      <c r="J29" s="188"/>
-      <c r="K29" s="188"/>
-      <c r="L29" s="188"/>
+      <c r="I29" s="195"/>
+      <c r="J29" s="195"/>
+      <c r="K29" s="195"/>
+      <c r="L29" s="195"/>
       <c r="M29" s="119">
         <v>0</v>
       </c>
@@ -4740,10 +4679,10 @@
       <c r="F30" s="116"/>
       <c r="G30" s="117"/>
       <c r="H30" s="118"/>
-      <c r="I30" s="188"/>
-      <c r="J30" s="188"/>
-      <c r="K30" s="188"/>
-      <c r="L30" s="188"/>
+      <c r="I30" s="195"/>
+      <c r="J30" s="195"/>
+      <c r="K30" s="195"/>
+      <c r="L30" s="195"/>
       <c r="M30" s="119">
         <v>40</v>
       </c>
@@ -4762,10 +4701,10 @@
       <c r="F31" s="116"/>
       <c r="G31" s="117"/>
       <c r="H31" s="118"/>
-      <c r="I31" s="188"/>
-      <c r="J31" s="188"/>
-      <c r="K31" s="188"/>
-      <c r="L31" s="188"/>
+      <c r="I31" s="195"/>
+      <c r="J31" s="195"/>
+      <c r="K31" s="195"/>
+      <c r="L31" s="195"/>
       <c r="M31" s="119">
         <v>40</v>
       </c>
@@ -4784,10 +4723,10 @@
       <c r="F32" s="116"/>
       <c r="G32" s="117"/>
       <c r="H32" s="118"/>
-      <c r="I32" s="188"/>
-      <c r="J32" s="188"/>
-      <c r="K32" s="188"/>
-      <c r="L32" s="188"/>
+      <c r="I32" s="195"/>
+      <c r="J32" s="195"/>
+      <c r="K32" s="195"/>
+      <c r="L32" s="195"/>
       <c r="M32" s="119">
         <v>160</v>
       </c>
@@ -4806,10 +4745,10 @@
       <c r="F33" s="116"/>
       <c r="G33" s="117"/>
       <c r="H33" s="118"/>
-      <c r="I33" s="188"/>
-      <c r="J33" s="188"/>
-      <c r="K33" s="188"/>
-      <c r="L33" s="188"/>
+      <c r="I33" s="195"/>
+      <c r="J33" s="195"/>
+      <c r="K33" s="195"/>
+      <c r="L33" s="195"/>
       <c r="M33" s="119">
         <v>0</v>
       </c>
@@ -4828,10 +4767,10 @@
       <c r="F34" s="116"/>
       <c r="G34" s="117"/>
       <c r="H34" s="118"/>
-      <c r="I34" s="188"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="188"/>
+      <c r="I34" s="195"/>
+      <c r="J34" s="195"/>
+      <c r="K34" s="195"/>
+      <c r="L34" s="195"/>
       <c r="M34" s="119">
         <v>100</v>
       </c>
@@ -4850,10 +4789,10 @@
       <c r="F35" s="116"/>
       <c r="G35" s="122"/>
       <c r="H35" s="118"/>
-      <c r="I35" s="188"/>
-      <c r="J35" s="188"/>
-      <c r="K35" s="188"/>
-      <c r="L35" s="188"/>
+      <c r="I35" s="195"/>
+      <c r="J35" s="195"/>
+      <c r="K35" s="195"/>
+      <c r="L35" s="195"/>
       <c r="M35" s="119">
         <v>0</v>
       </c>
@@ -4872,10 +4811,10 @@
       <c r="F36" s="116"/>
       <c r="G36" s="122"/>
       <c r="H36" s="118"/>
-      <c r="I36" s="188"/>
-      <c r="J36" s="188"/>
-      <c r="K36" s="188"/>
-      <c r="L36" s="188"/>
+      <c r="I36" s="195"/>
+      <c r="J36" s="195"/>
+      <c r="K36" s="195"/>
+      <c r="L36" s="195"/>
       <c r="M36" s="119">
         <v>0</v>
       </c>
@@ -4894,10 +4833,10 @@
       <c r="F37" s="116"/>
       <c r="G37" s="123"/>
       <c r="H37" s="118"/>
-      <c r="I37" s="188"/>
-      <c r="J37" s="188"/>
-      <c r="K37" s="188"/>
-      <c r="L37" s="188"/>
+      <c r="I37" s="195"/>
+      <c r="J37" s="195"/>
+      <c r="K37" s="195"/>
+      <c r="L37" s="195"/>
       <c r="M37" s="119">
         <v>0</v>
       </c>
@@ -4918,10 +4857,10 @@
       <c r="H38" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I38" s="188"/>
-      <c r="J38" s="188"/>
-      <c r="K38" s="188"/>
-      <c r="L38" s="188"/>
+      <c r="I38" s="195"/>
+      <c r="J38" s="195"/>
+      <c r="K38" s="195"/>
+      <c r="L38" s="195"/>
       <c r="M38" s="119">
         <v>0</v>
       </c>
@@ -4942,10 +4881,10 @@
       <c r="H39" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I39" s="188"/>
-      <c r="J39" s="188"/>
-      <c r="K39" s="188"/>
-      <c r="L39" s="188"/>
+      <c r="I39" s="195"/>
+      <c r="J39" s="195"/>
+      <c r="K39" s="195"/>
+      <c r="L39" s="195"/>
       <c r="M39" s="119">
         <v>40</v>
       </c>
@@ -4966,10 +4905,10 @@
       <c r="H40" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I40" s="188"/>
-      <c r="J40" s="188"/>
-      <c r="K40" s="188"/>
-      <c r="L40" s="188"/>
+      <c r="I40" s="195"/>
+      <c r="J40" s="195"/>
+      <c r="K40" s="195"/>
+      <c r="L40" s="195"/>
       <c r="M40" s="119">
         <v>40</v>
       </c>
@@ -4990,10 +4929,10 @@
       <c r="H41" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I41" s="188"/>
-      <c r="J41" s="188"/>
-      <c r="K41" s="188"/>
-      <c r="L41" s="188"/>
+      <c r="I41" s="195"/>
+      <c r="J41" s="195"/>
+      <c r="K41" s="195"/>
+      <c r="L41" s="195"/>
       <c r="M41" s="119">
         <v>0</v>
       </c>
@@ -5014,10 +4953,10 @@
       <c r="H42" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I42" s="188"/>
-      <c r="J42" s="188"/>
-      <c r="K42" s="188"/>
-      <c r="L42" s="188"/>
+      <c r="I42" s="195"/>
+      <c r="J42" s="195"/>
+      <c r="K42" s="195"/>
+      <c r="L42" s="195"/>
       <c r="M42" s="119">
         <v>0</v>
       </c>
@@ -5038,10 +4977,10 @@
       <c r="H43" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I43" s="188"/>
-      <c r="J43" s="188"/>
-      <c r="K43" s="188"/>
-      <c r="L43" s="188"/>
+      <c r="I43" s="195"/>
+      <c r="J43" s="195"/>
+      <c r="K43" s="195"/>
+      <c r="L43" s="195"/>
       <c r="M43" s="119">
         <v>0</v>
       </c>
@@ -5062,10 +5001,10 @@
       <c r="H44" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="I44" s="188"/>
-      <c r="J44" s="188"/>
-      <c r="K44" s="188"/>
-      <c r="L44" s="188"/>
+      <c r="I44" s="195"/>
+      <c r="J44" s="195"/>
+      <c r="K44" s="195"/>
+      <c r="L44" s="195"/>
       <c r="M44" s="119">
         <v>80</v>
       </c>
@@ -5086,10 +5025,10 @@
       <c r="H45" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="I45" s="203"/>
-      <c r="J45" s="203"/>
-      <c r="K45" s="203"/>
-      <c r="L45" s="203"/>
+      <c r="I45" s="196"/>
+      <c r="J45" s="196"/>
+      <c r="K45" s="196"/>
+      <c r="L45" s="196"/>
       <c r="M45" s="111">
         <v>80</v>
       </c>
@@ -5110,10 +5049,10 @@
       <c r="H46" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="I46" s="203"/>
-      <c r="J46" s="203"/>
-      <c r="K46" s="203"/>
-      <c r="L46" s="203"/>
+      <c r="I46" s="196"/>
+      <c r="J46" s="196"/>
+      <c r="K46" s="196"/>
+      <c r="L46" s="196"/>
       <c r="M46" s="111">
         <v>120</v>
       </c>
@@ -5134,10 +5073,10 @@
       <c r="H47" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="I47" s="203"/>
-      <c r="J47" s="203"/>
-      <c r="K47" s="203"/>
-      <c r="L47" s="203"/>
+      <c r="I47" s="196"/>
+      <c r="J47" s="196"/>
+      <c r="K47" s="196"/>
+      <c r="L47" s="196"/>
       <c r="M47" s="111"/>
       <c r="N47" s="102"/>
     </row>
@@ -5154,10 +5093,10 @@
       <c r="H48" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="I48" s="203"/>
-      <c r="J48" s="203"/>
-      <c r="K48" s="203"/>
-      <c r="L48" s="203"/>
+      <c r="I48" s="196"/>
+      <c r="J48" s="196"/>
+      <c r="K48" s="196"/>
+      <c r="L48" s="196"/>
       <c r="M48" s="111"/>
       <c r="N48" s="102"/>
     </row>
@@ -5174,10 +5113,10 @@
       <c r="H49" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="I49" s="194"/>
-      <c r="J49" s="194"/>
-      <c r="K49" s="194"/>
-      <c r="L49" s="194"/>
+      <c r="I49" s="202"/>
+      <c r="J49" s="202"/>
+      <c r="K49" s="202"/>
+      <c r="L49" s="202"/>
       <c r="M49" s="111"/>
       <c r="N49" s="109"/>
     </row>
@@ -5194,10 +5133,10 @@
       <c r="H50" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="I50" s="194"/>
-      <c r="J50" s="194"/>
-      <c r="K50" s="194"/>
-      <c r="L50" s="194"/>
+      <c r="I50" s="202"/>
+      <c r="J50" s="202"/>
+      <c r="K50" s="202"/>
+      <c r="L50" s="202"/>
       <c r="M50" s="111"/>
       <c r="N50" s="109"/>
     </row>
@@ -5238,77 +5177,77 @@
       <c r="D52" s="31"/>
     </row>
     <row r="53" spans="2:14" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="189" t="s">
+      <c r="B53" s="197" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="189"/>
-      <c r="D53" s="189"/>
-      <c r="E53" s="189"/>
-      <c r="F53" s="189"/>
-      <c r="G53" s="189"/>
-      <c r="H53" s="189"/>
-      <c r="I53" s="193" t="s">
+      <c r="C53" s="197"/>
+      <c r="D53" s="197"/>
+      <c r="E53" s="197"/>
+      <c r="F53" s="197"/>
+      <c r="G53" s="197"/>
+      <c r="H53" s="197"/>
+      <c r="I53" s="201" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="193"/>
-      <c r="K53" s="193"/>
-      <c r="L53" s="193"/>
+      <c r="J53" s="201"/>
+      <c r="K53" s="201"/>
+      <c r="L53" s="201"/>
       <c r="M53" s="66"/>
       <c r="N53" s="67"/>
     </row>
     <row r="54" spans="2:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="189"/>
-      <c r="C54" s="189"/>
-      <c r="D54" s="189"/>
-      <c r="E54" s="189"/>
-      <c r="F54" s="189"/>
-      <c r="G54" s="189"/>
-      <c r="H54" s="189"/>
-      <c r="I54" s="195" t="s">
+      <c r="B54" s="197"/>
+      <c r="C54" s="197"/>
+      <c r="D54" s="197"/>
+      <c r="E54" s="197"/>
+      <c r="F54" s="197"/>
+      <c r="G54" s="197"/>
+      <c r="H54" s="197"/>
+      <c r="I54" s="203" t="s">
         <v>84</v>
       </c>
-      <c r="J54" s="195"/>
-      <c r="K54" s="195"/>
-      <c r="L54" s="195"/>
+      <c r="J54" s="203"/>
+      <c r="K54" s="203"/>
+      <c r="L54" s="203"/>
       <c r="M54" s="47">
         <f>SUM(M15:M53)</f>
         <v>1320</v>
       </c>
-      <c r="N54" s="201"/>
+      <c r="N54" s="193"/>
     </row>
     <row r="55" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="189"/>
-      <c r="C55" s="189"/>
-      <c r="D55" s="189"/>
-      <c r="E55" s="189"/>
-      <c r="F55" s="189"/>
-      <c r="G55" s="189"/>
-      <c r="H55" s="189"/>
-      <c r="I55" s="195" t="s">
+      <c r="B55" s="197"/>
+      <c r="C55" s="197"/>
+      <c r="D55" s="197"/>
+      <c r="E55" s="197"/>
+      <c r="F55" s="197"/>
+      <c r="G55" s="197"/>
+      <c r="H55" s="197"/>
+      <c r="I55" s="203" t="s">
         <v>85</v>
       </c>
-      <c r="J55" s="195"/>
-      <c r="K55" s="195"/>
-      <c r="L55" s="195"/>
+      <c r="J55" s="203"/>
+      <c r="K55" s="203"/>
+      <c r="L55" s="203"/>
       <c r="M55" s="47">
         <v>0.25</v>
       </c>
-      <c r="N55" s="202"/>
+      <c r="N55" s="194"/>
     </row>
     <row r="56" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="189"/>
-      <c r="C56" s="189"/>
-      <c r="D56" s="189"/>
-      <c r="E56" s="189"/>
-      <c r="F56" s="189"/>
-      <c r="G56" s="189"/>
-      <c r="H56" s="189"/>
-      <c r="I56" s="195" t="s">
+      <c r="B56" s="197"/>
+      <c r="C56" s="197"/>
+      <c r="D56" s="197"/>
+      <c r="E56" s="197"/>
+      <c r="F56" s="197"/>
+      <c r="G56" s="197"/>
+      <c r="H56" s="197"/>
+      <c r="I56" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="J56" s="195"/>
-      <c r="K56" s="195"/>
-      <c r="L56" s="195"/>
+      <c r="J56" s="203"/>
+      <c r="K56" s="203"/>
+      <c r="L56" s="203"/>
       <c r="M56" s="47"/>
       <c r="N56" s="48">
         <f>SUM(N15:N55)</f>
@@ -5359,6 +5298,40 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="50">
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="B53:H56"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="I56:L56"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="I55:L55"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I16:L16"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="N54:N55"/>
@@ -5375,40 +5348,6 @@
     <mergeCell ref="I19:L19"/>
     <mergeCell ref="I32:L32"/>
     <mergeCell ref="I33:L33"/>
-    <mergeCell ref="B53:H56"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I56:L56"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="I55:L55"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
